--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122887465</v>
+        <v>122882954</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558046</v>
+        <v>557874</v>
       </c>
       <c r="R2" t="n">
-        <v>7045577</v>
+        <v>7045270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122887408</v>
+        <v>122885158</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +808,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558107</v>
+        <v>557925</v>
       </c>
       <c r="R3" t="n">
-        <v>7045485</v>
+        <v>7045226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122882954</v>
+        <v>122883501</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +929,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557874</v>
+        <v>557908</v>
       </c>
       <c r="R4" t="n">
-        <v>7045270</v>
+        <v>7045230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1132,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122883501</v>
+        <v>122887465</v>
       </c>
       <c r="B6" t="n">
-        <v>92225</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,25 +1153,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557908</v>
+        <v>558046</v>
       </c>
       <c r="R6" t="n">
-        <v>7045230</v>
+        <v>7045577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1366,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122885158</v>
+        <v>122887408</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,47 +1387,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557925</v>
+        <v>558107</v>
       </c>
       <c r="R8" t="n">
-        <v>7045226</v>
+        <v>7045485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122882954</v>
+        <v>122887288</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557874</v>
+        <v>558116</v>
       </c>
       <c r="R2" t="n">
-        <v>7045270</v>
+        <v>7045369</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885158</v>
+        <v>122883501</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557925</v>
+        <v>557908</v>
       </c>
       <c r="R3" t="n">
-        <v>7045226</v>
+        <v>7045230</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883501</v>
+        <v>122882954</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557908</v>
+        <v>557874</v>
       </c>
       <c r="R4" t="n">
-        <v>7045230</v>
+        <v>7045270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122887288</v>
+        <v>122885158</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1032,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558116</v>
+        <v>557925</v>
       </c>
       <c r="R5" t="n">
-        <v>7045369</v>
+        <v>7045226</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122887465</v>
+        <v>122887408</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,21 +1157,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558046</v>
+        <v>558107</v>
       </c>
       <c r="R6" t="n">
-        <v>7045577</v>
+        <v>7045485</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883141</v>
+        <v>122887465</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,39 +1269,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557872</v>
+        <v>558046</v>
       </c>
       <c r="R7" t="n">
-        <v>7045237</v>
+        <v>7045577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>+50 Ringhack på tall</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122887408</v>
+        <v>122883141</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1381,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558107</v>
+        <v>557872</v>
       </c>
       <c r="R8" t="n">
-        <v>7045485</v>
+        <v>7045237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1455,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>+50 Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,6 +1484,4387 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122908422</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>557977</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7045673</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122909860</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>558133</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7045474</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122914405</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92225</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>557976</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7045210</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122908738</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>558014</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7045616</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122914531</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>557870</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7045346</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122914213</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>557991</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7045335</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122909723</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Grössjörået, Grössjörået, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558113</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7045588</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122910006</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558154</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7045445</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122912795</v>
+      </c>
+      <c r="B17" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558128</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7045377</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122908181</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>557989</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7045623</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122908497</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>557969</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7045641</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122914308</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>557955</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7045351</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122908146</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>557988</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7045659</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122911743</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>558114</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7045374</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122914606</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90964</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>557893</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7045351</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122914334</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>557931</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7045323</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122909523</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Grössjörået, Grössjörået, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>558123</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7045531</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122909331</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>557986</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7045500</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122908532</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>557942</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7045683</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122908038</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>558017</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7045654</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122908440</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>557960</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7045650</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122914666</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>557892</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7045356</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122909987</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Grössjörået, Grössjörået, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>558129</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7045578</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122910281</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grössjörået, Grössjörået, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>558178</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7045498</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122908246</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>557977</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7045628</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122908666</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>557951</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7045711</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122909049</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>558048</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7045527</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122908779</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>557996</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7045609</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122909181</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>558033</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7045487</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122909459</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>557966</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7045501</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122908447</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>557958</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7045677</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122908559</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>557959</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7045628</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122908377</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>557960</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7045662</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122912661</v>
+      </c>
+      <c r="B42" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>558113</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7045372</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122913820</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>558157</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7045329</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122914573</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>557892</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7045361</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122914868</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79848</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>557948</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7045384</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122914413</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>557884</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7045302</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -1945,7 +1945,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122914531</v>
+        <v>122914213</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557870</v>
+        <v>557991</v>
       </c>
       <c r="R13" t="n">
-        <v>7045346</v>
+        <v>7045335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,7 +2057,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122914213</v>
+        <v>122914531</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557991</v>
+        <v>557870</v>
       </c>
       <c r="R14" t="n">
-        <v>7045335</v>
+        <v>7045346</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2281,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122910006</v>
+        <v>122908181</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,38 +2293,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558154</v>
+        <v>557989</v>
       </c>
       <c r="R16" t="n">
-        <v>7045445</v>
+        <v>7045623</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2360,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2370,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,22 +2385,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122912795</v>
+        <v>122910006</v>
       </c>
       <c r="B17" t="n">
-        <v>82553</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,21 +2413,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2433,10 +2437,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558128</v>
+        <v>558154</v>
       </c>
       <c r="R17" t="n">
-        <v>7045377</v>
+        <v>7045445</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,7 +2472,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2482,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,19 +2497,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122908181</v>
+        <v>122908497</v>
       </c>
       <c r="B18" t="n">
         <v>98357</v>
@@ -2540,19 +2544,24 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557989</v>
+        <v>557969</v>
       </c>
       <c r="R18" t="n">
-        <v>7045623</v>
+        <v>7045641</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,7 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2609,22 +2618,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122908497</v>
+        <v>122912795</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>82553</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,47 +2642,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557969</v>
+        <v>558128</v>
       </c>
       <c r="R19" t="n">
-        <v>7045641</v>
+        <v>7045377</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,12 +2730,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122908440</v>
+        <v>122914666</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3813,19 +3813,19 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557960</v>
+        <v>557892</v>
       </c>
       <c r="R29" t="n">
-        <v>7045650</v>
+        <v>7045356</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3887,19 +3887,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122914666</v>
+        <v>122908440</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3935,19 +3935,19 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557892</v>
+        <v>557960</v>
       </c>
       <c r="R30" t="n">
-        <v>7045356</v>
+        <v>7045650</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122908422</v>
+        <v>122914405</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>92225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,43 +1499,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557977</v>
+        <v>557976</v>
       </c>
       <c r="R9" t="n">
-        <v>7045673</v>
+        <v>7045210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122909860</v>
+        <v>122908422</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,34 +1615,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558133</v>
+        <v>557977</v>
       </c>
       <c r="R10" t="n">
-        <v>7045474</v>
+        <v>7045673</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,7 +1689,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,22 +1709,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122914405</v>
+        <v>122909860</v>
       </c>
       <c r="B11" t="n">
-        <v>92225</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,25 +1733,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557976</v>
+        <v>558133</v>
       </c>
       <c r="R11" t="n">
-        <v>7045210</v>
+        <v>7045474</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3777,7 +3777,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122914666</v>
+        <v>122908440</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3813,19 +3813,19 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557892</v>
+        <v>557960</v>
       </c>
       <c r="R29" t="n">
-        <v>7045356</v>
+        <v>7045650</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3887,19 +3887,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122908440</v>
+        <v>122914666</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3935,19 +3935,19 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557960</v>
+        <v>557892</v>
       </c>
       <c r="R30" t="n">
-        <v>7045650</v>
+        <v>7045356</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4009,12 +4009,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122908666</v>
+        <v>122909049</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4377,34 +4377,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557951</v>
+        <v>558048</v>
       </c>
       <c r="R34" t="n">
-        <v>7045711</v>
+        <v>7045527</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4436,7 +4441,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4446,7 +4451,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4461,22 +4471,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122909049</v>
+        <v>122908666</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4489,39 +4499,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558048</v>
+        <v>557951</v>
       </c>
       <c r="R35" t="n">
-        <v>7045527</v>
+        <v>7045711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4553,7 +4558,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4563,12 +4568,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4583,12 +4583,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -2281,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122908181</v>
+        <v>122910006</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,42 +2293,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557989</v>
+        <v>558154</v>
       </c>
       <c r="R16" t="n">
-        <v>7045623</v>
+        <v>7045445</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2370,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,22 +2381,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122910006</v>
+        <v>122908497</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,38 +2405,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558154</v>
+        <v>557969</v>
       </c>
       <c r="R17" t="n">
-        <v>7045445</v>
+        <v>7045641</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122908497</v>
+        <v>122912795</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>82553</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,47 +2526,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557969</v>
+        <v>558128</v>
       </c>
       <c r="R18" t="n">
-        <v>7045641</v>
+        <v>7045377</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,22 +2614,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122912795</v>
+        <v>122908181</v>
       </c>
       <c r="B19" t="n">
-        <v>82553</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,38 +2638,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558128</v>
+        <v>557989</v>
       </c>
       <c r="R19" t="n">
-        <v>7045377</v>
+        <v>7045623</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3082,10 +3082,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122914606</v>
+        <v>122914334</v>
       </c>
       <c r="B23" t="n">
-        <v>90964</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,21 +3098,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557893</v>
+        <v>557931</v>
       </c>
       <c r="R23" t="n">
-        <v>7045351</v>
+        <v>7045323</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3194,10 +3194,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122914334</v>
+        <v>122914606</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>90964</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557931</v>
+        <v>557893</v>
       </c>
       <c r="R24" t="n">
-        <v>7045323</v>
+        <v>7045351</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122887288</v>
+        <v>122887465</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558116</v>
+        <v>558046</v>
       </c>
       <c r="R2" t="n">
-        <v>7045369</v>
+        <v>7045577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122882954</v>
+        <v>122885158</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -934,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557874</v>
+        <v>557925</v>
       </c>
       <c r="R4" t="n">
-        <v>7045270</v>
+        <v>7045226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122885158</v>
+        <v>122887408</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,47 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557925</v>
+        <v>558107</v>
       </c>
       <c r="R5" t="n">
-        <v>7045226</v>
+        <v>7045485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122887408</v>
+        <v>122887288</v>
       </c>
       <c r="B6" t="n">
         <v>79847</v>
@@ -1181,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558107</v>
+        <v>558116</v>
       </c>
       <c r="R6" t="n">
-        <v>7045485</v>
+        <v>7045369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122887465</v>
+        <v>122882954</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,38 +1256,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558046</v>
+        <v>557874</v>
       </c>
       <c r="R7" t="n">
-        <v>7045577</v>
+        <v>7045270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122914405</v>
+        <v>122909459</v>
       </c>
       <c r="B9" t="n">
-        <v>92225</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,38 +1499,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557976</v>
+        <v>557966</v>
       </c>
       <c r="R9" t="n">
-        <v>7045210</v>
+        <v>7045501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122908422</v>
+        <v>122908779</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,43 +1621,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557977</v>
+        <v>557996</v>
       </c>
       <c r="R10" t="n">
-        <v>7045673</v>
+        <v>7045609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,12 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122909860</v>
+        <v>122914868</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1761,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558133</v>
+        <v>557948</v>
       </c>
       <c r="R11" t="n">
-        <v>7045474</v>
+        <v>7045384</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,22 +1825,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122908738</v>
+        <v>122908440</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,34 +1853,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558014</v>
+        <v>557960</v>
       </c>
       <c r="R12" t="n">
-        <v>7045616</v>
+        <v>7045650</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1918,7 +1927,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1945,10 +1959,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122914213</v>
+        <v>122909049</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1961,34 +1975,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557991</v>
+        <v>558048</v>
       </c>
       <c r="R13" t="n">
-        <v>7045335</v>
+        <v>7045527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2039,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2049,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,22 +2069,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122914531</v>
+        <v>122908146</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,38 +2093,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557870</v>
+        <v>557988</v>
       </c>
       <c r="R14" t="n">
-        <v>7045346</v>
+        <v>7045659</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2132,7 +2160,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +2170,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,7 +2197,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122909723</v>
+        <v>122914573</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2205,14 +2233,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558113</v>
+        <v>557892</v>
       </c>
       <c r="R15" t="n">
-        <v>7045588</v>
+        <v>7045361</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2272,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2282,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,7 +2309,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122910006</v>
+        <v>122911743</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2321,10 +2349,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558154</v>
+        <v>558114</v>
       </c>
       <c r="R16" t="n">
-        <v>7045445</v>
+        <v>7045374</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2384,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2394,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,10 +2421,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908497</v>
+        <v>122914405</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>92225</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,47 +2433,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557969</v>
+        <v>557976</v>
       </c>
       <c r="R17" t="n">
-        <v>7045641</v>
+        <v>7045210</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,7 +2496,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2506,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2533,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122912795</v>
+        <v>122909723</v>
       </c>
       <c r="B18" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,34 +2549,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558128</v>
+        <v>558113</v>
       </c>
       <c r="R18" t="n">
-        <v>7045377</v>
+        <v>7045588</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,7 +2608,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2618,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,10 +2645,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122908181</v>
+        <v>122908447</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2638,42 +2657,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557989</v>
+        <v>557958</v>
       </c>
       <c r="R19" t="n">
-        <v>7045623</v>
+        <v>7045677</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2730,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122914308</v>
+        <v>122913820</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,38 +2769,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557955</v>
+        <v>558157</v>
       </c>
       <c r="R20" t="n">
-        <v>7045351</v>
+        <v>7045329</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2817,7 +2836,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2827,7 +2846,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122908146</v>
+        <v>122912661</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>82553</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2866,42 +2885,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557988</v>
+        <v>558113</v>
       </c>
       <c r="R21" t="n">
-        <v>7045659</v>
+        <v>7045372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2933,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2943,7 +2958,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122911743</v>
+        <v>122908422</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,34 +3001,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558114</v>
+        <v>557977</v>
       </c>
       <c r="R22" t="n">
-        <v>7045374</v>
+        <v>7045673</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3045,7 +3065,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3055,7 +3075,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,19 +3095,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122914334</v>
+        <v>122914308</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -3122,10 +3147,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557931</v>
+        <v>557955</v>
       </c>
       <c r="R23" t="n">
-        <v>7045323</v>
+        <v>7045351</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3157,7 +3182,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3167,7 +3192,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3194,10 +3219,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122914606</v>
+        <v>122909181</v>
       </c>
       <c r="B24" t="n">
-        <v>90964</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3206,38 +3231,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557893</v>
+        <v>558033</v>
       </c>
       <c r="R24" t="n">
-        <v>7045351</v>
+        <v>7045487</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3269,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3279,7 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3294,22 +3328,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122909523</v>
+        <v>122908738</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3318,42 +3352,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558123</v>
+        <v>558014</v>
       </c>
       <c r="R25" t="n">
-        <v>7045531</v>
+        <v>7045616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3385,7 +3415,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3425,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3410,22 +3440,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122909331</v>
+        <v>122908559</v>
       </c>
       <c r="B26" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3438,16 +3468,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3467,10 +3497,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557986</v>
+        <v>557959</v>
       </c>
       <c r="R26" t="n">
-        <v>7045500</v>
+        <v>7045628</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3502,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3512,7 +3542,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,10 +3574,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122908532</v>
+        <v>122914606</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>90964</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3551,42 +3586,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557942</v>
+        <v>557893</v>
       </c>
       <c r="R27" t="n">
-        <v>7045683</v>
+        <v>7045351</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3618,7 +3649,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3628,7 +3659,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3655,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122908038</v>
+        <v>122908497</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3667,31 +3698,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3700,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558017</v>
+        <v>557969</v>
       </c>
       <c r="R28" t="n">
-        <v>7045654</v>
+        <v>7045641</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3735,7 +3770,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,12 +3780,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3765,22 +3795,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122908440</v>
+        <v>122909331</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3793,16 +3823,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3818,14 +3848,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557960</v>
+        <v>557986</v>
       </c>
       <c r="R29" t="n">
-        <v>7045650</v>
+        <v>7045500</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3857,7 +3887,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3867,12 +3897,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4021,10 +4046,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122909987</v>
+        <v>122908377</v>
       </c>
       <c r="B31" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4037,34 +4062,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558129</v>
+        <v>557960</v>
       </c>
       <c r="R31" t="n">
-        <v>7045578</v>
+        <v>7045662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4096,7 +4121,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4106,7 +4131,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4133,10 +4158,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122910281</v>
+        <v>122908181</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4145,38 +4170,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558178</v>
+        <v>557989</v>
       </c>
       <c r="R32" t="n">
-        <v>7045498</v>
+        <v>7045623</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4208,7 +4237,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4218,7 +4247,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4245,10 +4274,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122908246</v>
+        <v>122908532</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4257,42 +4286,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557977</v>
+        <v>557942</v>
       </c>
       <c r="R33" t="n">
-        <v>7045628</v>
+        <v>7045683</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4324,7 +4353,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4334,7 +4363,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4361,10 +4390,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122909049</v>
+        <v>122910006</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4377,39 +4406,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558048</v>
+        <v>558154</v>
       </c>
       <c r="R34" t="n">
-        <v>7045527</v>
+        <v>7045445</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4441,7 +4465,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4451,12 +4475,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4483,10 +4502,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122908666</v>
+        <v>122914413</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4495,38 +4514,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557951</v>
+        <v>557884</v>
       </c>
       <c r="R35" t="n">
-        <v>7045711</v>
+        <v>7045302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4558,7 +4581,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4568,7 +4591,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4595,10 +4618,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122908779</v>
+        <v>122908666</v>
       </c>
       <c r="B36" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4607,42 +4630,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557996</v>
+        <v>557951</v>
       </c>
       <c r="R36" t="n">
-        <v>7045609</v>
+        <v>7045711</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4674,7 +4693,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4684,7 +4703,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4711,10 +4730,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122909181</v>
+        <v>122912795</v>
       </c>
       <c r="B37" t="n">
-        <v>98357</v>
+        <v>82553</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4723,47 +4742,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558033</v>
+        <v>558128</v>
       </c>
       <c r="R37" t="n">
-        <v>7045487</v>
+        <v>7045377</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4795,7 +4805,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4805,7 +4815,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4820,19 +4830,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122909459</v>
+        <v>122908246</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -4865,10 +4875,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4877,10 +4886,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557966</v>
+        <v>557977</v>
       </c>
       <c r="R38" t="n">
-        <v>7045501</v>
+        <v>7045628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4912,7 +4921,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4922,12 +4931,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4942,19 +4946,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122908447</v>
+        <v>122914531</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4990,14 +4994,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557958</v>
+        <v>557870</v>
       </c>
       <c r="R39" t="n">
-        <v>7045677</v>
+        <v>7045346</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5029,7 +5033,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5039,7 +5043,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5066,10 +5070,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122908559</v>
+        <v>122914213</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5082,39 +5086,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557959</v>
+        <v>557991</v>
       </c>
       <c r="R40" t="n">
-        <v>7045628</v>
+        <v>7045335</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5146,7 +5145,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5156,12 +5155,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5176,22 +5170,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122908377</v>
+        <v>122909523</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5200,38 +5194,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557960</v>
+        <v>558123</v>
       </c>
       <c r="R41" t="n">
-        <v>7045662</v>
+        <v>7045531</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5263,7 +5261,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5273,7 +5271,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5300,10 +5298,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122912661</v>
+        <v>122909987</v>
       </c>
       <c r="B42" t="n">
-        <v>82553</v>
+        <v>90944</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5316,34 +5314,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558113</v>
+        <v>558129</v>
       </c>
       <c r="R42" t="n">
-        <v>7045372</v>
+        <v>7045578</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5375,7 +5373,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5385,7 +5383,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5412,10 +5410,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122913820</v>
+        <v>122914334</v>
       </c>
       <c r="B43" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5424,42 +5422,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558157</v>
+        <v>557931</v>
       </c>
       <c r="R43" t="n">
-        <v>7045329</v>
+        <v>7045323</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5491,7 +5485,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5501,7 +5495,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5528,10 +5522,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122914573</v>
+        <v>122909860</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5544,21 +5538,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5568,10 +5562,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557892</v>
+        <v>558133</v>
       </c>
       <c r="R44" t="n">
-        <v>7045361</v>
+        <v>7045474</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5603,7 +5597,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5613,7 +5607,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5628,22 +5622,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122914868</v>
+        <v>122910281</v>
       </c>
       <c r="B45" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5656,34 +5650,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557948</v>
+        <v>558178</v>
       </c>
       <c r="R45" t="n">
-        <v>7045384</v>
+        <v>7045498</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5715,7 +5709,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5725,7 +5719,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5752,10 +5746,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122914413</v>
+        <v>122908038</v>
       </c>
       <c r="B46" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5764,42 +5758,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557884</v>
+        <v>558017</v>
       </c>
       <c r="R46" t="n">
-        <v>7045302</v>
+        <v>7045654</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5831,7 +5826,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5841,7 +5836,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122909459</v>
+        <v>122908779</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,31 +1499,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1532,10 +1531,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557966</v>
+        <v>557996</v>
       </c>
       <c r="R9" t="n">
-        <v>7045501</v>
+        <v>7045609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,22 +1591,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122908779</v>
+        <v>122909459</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,30 +1615,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557996</v>
+        <v>557966</v>
       </c>
       <c r="R10" t="n">
-        <v>7045609</v>
+        <v>7045501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1693,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,12 +1713,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122908497</v>
+        <v>122909331</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3698,47 +3698,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557969</v>
+        <v>557986</v>
       </c>
       <c r="R28" t="n">
-        <v>7045641</v>
+        <v>7045500</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3770,7 +3766,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3780,7 +3776,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3807,10 +3803,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122909331</v>
+        <v>122908377</v>
       </c>
       <c r="B29" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3823,39 +3819,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557986</v>
+        <v>557960</v>
       </c>
       <c r="R29" t="n">
-        <v>7045500</v>
+        <v>7045662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3887,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3897,7 +3888,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,12 +3903,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4046,10 +4037,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122908377</v>
+        <v>122908497</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4058,38 +4049,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557960</v>
+        <v>557969</v>
       </c>
       <c r="R31" t="n">
-        <v>7045662</v>
+        <v>7045641</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4146,12 +4146,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122909523</v>
+        <v>122914334</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5194,42 +5194,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558123</v>
+        <v>557931</v>
       </c>
       <c r="R41" t="n">
-        <v>7045531</v>
+        <v>7045323</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5261,7 +5257,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5271,7 +5267,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5298,10 +5294,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122909987</v>
+        <v>122909860</v>
       </c>
       <c r="B42" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5314,34 +5310,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558129</v>
+        <v>558133</v>
       </c>
       <c r="R42" t="n">
-        <v>7045578</v>
+        <v>7045474</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5373,7 +5369,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5383,7 +5379,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5398,22 +5394,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122914334</v>
+        <v>122909523</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5422,38 +5418,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557931</v>
+        <v>558123</v>
       </c>
       <c r="R43" t="n">
-        <v>7045323</v>
+        <v>7045531</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5522,10 +5522,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122909860</v>
+        <v>122909987</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5538,34 +5538,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558133</v>
+        <v>558129</v>
       </c>
       <c r="R44" t="n">
-        <v>7045474</v>
+        <v>7045578</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5622,12 +5622,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122908779</v>
+        <v>122909459</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,30 +1499,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1531,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557996</v>
+        <v>557966</v>
       </c>
       <c r="R9" t="n">
-        <v>7045609</v>
+        <v>7045501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,22 +1597,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122909459</v>
+        <v>122908779</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,31 +1621,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557966</v>
+        <v>557996</v>
       </c>
       <c r="R10" t="n">
-        <v>7045501</v>
+        <v>7045609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,12 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,22 +1713,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122914868</v>
+        <v>122908440</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,34 +1741,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557948</v>
+        <v>557960</v>
       </c>
       <c r="R11" t="n">
-        <v>7045384</v>
+        <v>7045650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1815,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,19 +1835,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122908440</v>
+        <v>122909049</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1873,19 +1883,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557960</v>
+        <v>558048</v>
       </c>
       <c r="R12" t="n">
-        <v>7045650</v>
+        <v>7045527</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,7 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1959,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122909049</v>
+        <v>122914868</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,39 +1985,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558048</v>
+        <v>557948</v>
       </c>
       <c r="R13" t="n">
-        <v>7045527</v>
+        <v>7045384</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,12 +2054,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,12 +2069,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122908447</v>
+        <v>122913820</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2657,38 +2657,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557958</v>
+        <v>558157</v>
       </c>
       <c r="R19" t="n">
-        <v>7045677</v>
+        <v>7045329</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122913820</v>
+        <v>122908447</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2769,42 +2773,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558157</v>
+        <v>557958</v>
       </c>
       <c r="R20" t="n">
-        <v>7045329</v>
+        <v>7045677</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2985,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122908422</v>
+        <v>122914308</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,39 +3001,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557977</v>
+        <v>557955</v>
       </c>
       <c r="R22" t="n">
-        <v>7045673</v>
+        <v>7045351</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3065,7 +3060,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3075,12 +3070,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122914308</v>
+        <v>122908422</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,34 +3113,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557955</v>
+        <v>557977</v>
       </c>
       <c r="R23" t="n">
-        <v>7045351</v>
+        <v>7045673</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3182,7 +3177,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3192,7 +3187,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -5182,10 +5182,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122914334</v>
+        <v>122909523</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5194,38 +5194,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557931</v>
+        <v>558123</v>
       </c>
       <c r="R41" t="n">
-        <v>7045323</v>
+        <v>7045531</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5257,7 +5261,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5267,7 +5271,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5294,10 +5298,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122909860</v>
+        <v>122909987</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5310,34 +5314,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558133</v>
+        <v>558129</v>
       </c>
       <c r="R42" t="n">
-        <v>7045474</v>
+        <v>7045578</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5369,7 +5373,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5379,7 +5383,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5394,22 +5398,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122909523</v>
+        <v>122914334</v>
       </c>
       <c r="B43" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5418,42 +5422,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558123</v>
+        <v>557931</v>
       </c>
       <c r="R43" t="n">
-        <v>7045531</v>
+        <v>7045323</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5522,10 +5522,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122909987</v>
+        <v>122909860</v>
       </c>
       <c r="B44" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5538,34 +5538,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558129</v>
+        <v>558133</v>
       </c>
       <c r="R44" t="n">
-        <v>7045578</v>
+        <v>7045474</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5622,12 +5622,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5866,6 +5866,1022 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123116920</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78150</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>557888</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7045356</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123119791</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>557988</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7045172</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123114009</v>
+      </c>
+      <c r="B49" t="n">
+        <v>90917</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>558050</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7045576</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123117683</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78502</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>557966</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7045239</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123115068</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>557961</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7045587</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123117651</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57589</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>557907</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7045262</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123115166</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78411</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>353</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>557961</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7045574</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123115087</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>557957</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7045576</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>123114354</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>557978</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7045589</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122887465</v>
+        <v>122887288</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558046</v>
+        <v>558116</v>
       </c>
       <c r="R2" t="n">
-        <v>7045577</v>
+        <v>7045369</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883501</v>
+        <v>122883141</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557908</v>
+        <v>557872</v>
       </c>
       <c r="R3" t="n">
-        <v>7045230</v>
+        <v>7045237</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>+50 Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122885158</v>
+        <v>122887408</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557925</v>
+        <v>558107</v>
       </c>
       <c r="R4" t="n">
-        <v>7045226</v>
+        <v>7045485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122887408</v>
+        <v>122885158</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1033,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558107</v>
+        <v>557925</v>
       </c>
       <c r="R5" t="n">
-        <v>7045485</v>
+        <v>7045226</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122887288</v>
+        <v>122887465</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558116</v>
+        <v>558046</v>
       </c>
       <c r="R6" t="n">
-        <v>7045369</v>
+        <v>7045577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122882954</v>
+        <v>122883501</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>92233</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,47 +1266,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557874</v>
+        <v>557908</v>
       </c>
       <c r="R7" t="n">
-        <v>7045270</v>
+        <v>7045230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122883141</v>
+        <v>122882954</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,31 +1378,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1410,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557872</v>
+        <v>557874</v>
       </c>
       <c r="R8" t="n">
-        <v>7045237</v>
+        <v>7045270</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,12 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>+50 Ringhack på tall</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1609,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122908779</v>
+        <v>122909181</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,7 +1644,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557996</v>
+        <v>558033</v>
       </c>
       <c r="R10" t="n">
-        <v>7045609</v>
+        <v>7045487</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1693,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1703,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,22 +1718,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122908440</v>
+        <v>122914606</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>90972</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,39 +1746,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557960</v>
+        <v>557893</v>
       </c>
       <c r="R11" t="n">
-        <v>7045650</v>
+        <v>7045351</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,12 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,22 +1830,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122909049</v>
+        <v>122909523</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,43 +1854,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558048</v>
+        <v>558123</v>
       </c>
       <c r="R12" t="n">
-        <v>7045527</v>
+        <v>7045531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,12 +1931,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,22 +1946,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122914868</v>
+        <v>122914531</v>
       </c>
       <c r="B13" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,21 +1974,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,10 +1998,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557948</v>
+        <v>557870</v>
       </c>
       <c r="R13" t="n">
-        <v>7045384</v>
+        <v>7045346</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,7 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122908146</v>
+        <v>122914405</v>
       </c>
       <c r="B14" t="n">
-        <v>98357</v>
+        <v>92233</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,42 +2082,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557988</v>
+        <v>557976</v>
       </c>
       <c r="R14" t="n">
-        <v>7045659</v>
+        <v>7045210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,19 +2170,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122914573</v>
+        <v>122910281</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2233,14 +2218,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557892</v>
+        <v>558178</v>
       </c>
       <c r="R15" t="n">
-        <v>7045361</v>
+        <v>7045498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122911743</v>
+        <v>122909331</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,34 +2310,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558114</v>
+        <v>557986</v>
       </c>
       <c r="R16" t="n">
-        <v>7045374</v>
+        <v>7045500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2384,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2394,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2421,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122914405</v>
+        <v>122908181</v>
       </c>
       <c r="B17" t="n">
-        <v>92225</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2433,38 +2423,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557976</v>
+        <v>557989</v>
       </c>
       <c r="R17" t="n">
-        <v>7045210</v>
+        <v>7045623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2496,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2506,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,22 +2515,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122909723</v>
+        <v>122913820</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2545,38 +2539,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558113</v>
+        <v>558157</v>
       </c>
       <c r="R18" t="n">
-        <v>7045588</v>
+        <v>7045329</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2608,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2618,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2645,10 +2643,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122913820</v>
+        <v>122909987</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>90952</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2657,42 +2655,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558157</v>
+        <v>558129</v>
       </c>
       <c r="R19" t="n">
-        <v>7045329</v>
+        <v>7045578</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,7 +2718,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2728,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,10 +2755,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122908447</v>
+        <v>122912661</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2777,34 +2771,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557958</v>
+        <v>558113</v>
       </c>
       <c r="R20" t="n">
-        <v>7045677</v>
+        <v>7045372</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,7 +2830,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2840,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,10 +2867,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122912661</v>
+        <v>122908440</v>
       </c>
       <c r="B21" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,34 +2883,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558113</v>
+        <v>557960</v>
       </c>
       <c r="R21" t="n">
-        <v>7045372</v>
+        <v>7045650</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2947,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,7 +2957,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,22 +2977,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122914308</v>
+        <v>122908532</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,38 +3001,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557955</v>
+        <v>557942</v>
       </c>
       <c r="R22" t="n">
-        <v>7045351</v>
+        <v>7045683</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3060,7 +3068,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3070,7 +3078,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,10 +3105,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122908422</v>
+        <v>122914573</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,39 +3121,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557977</v>
+        <v>557892</v>
       </c>
       <c r="R23" t="n">
-        <v>7045673</v>
+        <v>7045361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3177,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3187,12 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,10 +3217,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122909181</v>
+        <v>122908779</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3254,12 +3252,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3268,10 +3261,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558033</v>
+        <v>557996</v>
       </c>
       <c r="R24" t="n">
-        <v>7045487</v>
+        <v>7045609</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,19 +3321,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122908738</v>
+        <v>122909860</v>
       </c>
       <c r="B25" t="n">
         <v>79847</v>
@@ -3380,10 +3373,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558014</v>
+        <v>558133</v>
       </c>
       <c r="R25" t="n">
-        <v>7045616</v>
+        <v>7045474</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3415,7 +3408,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3425,7 +3418,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3452,10 +3445,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122908559</v>
+        <v>122908666</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3468,39 +3461,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557959</v>
+        <v>557951</v>
       </c>
       <c r="R26" t="n">
-        <v>7045628</v>
+        <v>7045711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3532,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,12 +3530,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3562,22 +3545,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122914606</v>
+        <v>122908422</v>
       </c>
       <c r="B27" t="n">
-        <v>90964</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,34 +3573,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557893</v>
+        <v>557977</v>
       </c>
       <c r="R27" t="n">
-        <v>7045351</v>
+        <v>7045673</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3649,7 +3637,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3659,7 +3647,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,10 +3679,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122909331</v>
+        <v>122908559</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3702,16 +3695,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3731,10 +3724,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557986</v>
+        <v>557959</v>
       </c>
       <c r="R28" t="n">
-        <v>7045500</v>
+        <v>7045628</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3766,7 +3759,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3776,7 +3769,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3915,7 +3913,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122914666</v>
+        <v>122908038</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3951,19 +3949,19 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557892</v>
+        <v>558017</v>
       </c>
       <c r="R30" t="n">
-        <v>7045356</v>
+        <v>7045654</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3995,7 +3993,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4005,12 +4003,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4037,10 +4035,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122908497</v>
+        <v>122912795</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>82553</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4049,47 +4047,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557969</v>
+        <v>558128</v>
       </c>
       <c r="R31" t="n">
-        <v>7045641</v>
+        <v>7045377</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4121,7 +4110,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4131,7 +4120,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4146,22 +4135,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122908181</v>
+        <v>122908738</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4170,42 +4159,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557989</v>
+        <v>558014</v>
       </c>
       <c r="R32" t="n">
-        <v>7045623</v>
+        <v>7045616</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4237,7 +4222,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4247,7 +4232,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4262,22 +4247,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122908532</v>
+        <v>122914666</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4286,42 +4271,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557942</v>
+        <v>557892</v>
       </c>
       <c r="R33" t="n">
-        <v>7045683</v>
+        <v>7045356</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4353,7 +4339,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4363,7 +4349,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4390,10 +4381,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122910006</v>
+        <v>122908246</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4406,34 +4397,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558154</v>
+        <v>557977</v>
       </c>
       <c r="R34" t="n">
-        <v>7045445</v>
+        <v>7045628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4465,7 +4460,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4475,7 +4470,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4490,22 +4485,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122914413</v>
+        <v>122910006</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4514,42 +4509,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557884</v>
+        <v>558154</v>
       </c>
       <c r="R35" t="n">
-        <v>7045302</v>
+        <v>7045445</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4581,7 +4572,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4591,7 +4582,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4606,19 +4597,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122908666</v>
+        <v>122914213</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4654,14 +4645,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557951</v>
+        <v>557991</v>
       </c>
       <c r="R36" t="n">
-        <v>7045711</v>
+        <v>7045335</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4693,7 +4684,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4703,7 +4694,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4730,10 +4721,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122912795</v>
+        <v>122914334</v>
       </c>
       <c r="B37" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4746,21 +4737,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4770,10 +4761,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558128</v>
+        <v>557931</v>
       </c>
       <c r="R37" t="n">
-        <v>7045377</v>
+        <v>7045323</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4805,7 +4796,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4815,7 +4806,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4842,10 +4833,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122908246</v>
+        <v>122914413</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4854,30 +4845,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4886,10 +4877,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557977</v>
+        <v>557884</v>
       </c>
       <c r="R38" t="n">
-        <v>7045628</v>
+        <v>7045302</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4921,7 +4912,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4931,7 +4922,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4958,10 +4949,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122914531</v>
+        <v>122914868</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4974,21 +4965,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4998,10 +4989,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557870</v>
+        <v>557948</v>
       </c>
       <c r="R39" t="n">
-        <v>7045346</v>
+        <v>7045384</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5033,7 +5024,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5043,7 +5034,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5070,10 +5061,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122914213</v>
+        <v>122908146</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5082,38 +5073,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557991</v>
+        <v>557988</v>
       </c>
       <c r="R40" t="n">
-        <v>7045335</v>
+        <v>7045659</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5145,7 +5140,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5150,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5182,10 +5177,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122909523</v>
+        <v>122911743</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5194,42 +5189,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558123</v>
+        <v>558114</v>
       </c>
       <c r="R41" t="n">
-        <v>7045531</v>
+        <v>7045374</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5261,7 +5252,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5271,7 +5262,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5286,22 +5277,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122909987</v>
+        <v>122914308</v>
       </c>
       <c r="B42" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5314,34 +5305,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558129</v>
+        <v>557955</v>
       </c>
       <c r="R42" t="n">
-        <v>7045578</v>
+        <v>7045351</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5373,7 +5364,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5383,7 +5374,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5410,7 +5401,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122914334</v>
+        <v>122909723</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -5446,14 +5437,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557931</v>
+        <v>558113</v>
       </c>
       <c r="R43" t="n">
-        <v>7045323</v>
+        <v>7045588</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5485,7 +5476,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5495,7 +5486,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5522,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122909860</v>
+        <v>122908497</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5534,38 +5525,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558133</v>
+        <v>557969</v>
       </c>
       <c r="R44" t="n">
-        <v>7045474</v>
+        <v>7045641</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5634,7 +5634,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122910281</v>
+        <v>122908447</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5670,14 +5670,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558178</v>
+        <v>557958</v>
       </c>
       <c r="R45" t="n">
-        <v>7045498</v>
+        <v>7045677</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5746,7 +5746,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122908038</v>
+        <v>122909049</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5782,19 +5782,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558017</v>
+        <v>558048</v>
       </c>
       <c r="R46" t="n">
-        <v>7045654</v>
+        <v>7045527</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5856,22 +5856,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123116920</v>
+        <v>123115166</v>
       </c>
       <c r="B47" t="n">
-        <v>78150</v>
+        <v>78411</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5884,21 +5884,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557888</v>
+        <v>557961</v>
       </c>
       <c r="R47" t="n">
-        <v>7045356</v>
+        <v>7045574</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5941,9 +5941,19 @@
           <t>2025-03-12</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5958,22 +5968,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123119791</v>
+        <v>123117651</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>57589</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5982,30 +5992,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6014,10 +6029,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557988</v>
+        <v>557907</v>
       </c>
       <c r="R48" t="n">
-        <v>7045172</v>
+        <v>7045262</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6049,7 +6064,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6059,7 +6074,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6086,10 +6101,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123114009</v>
+        <v>123117683</v>
       </c>
       <c r="B49" t="n">
-        <v>90917</v>
+        <v>78502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6098,25 +6113,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6126,10 +6141,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558050</v>
+        <v>557966</v>
       </c>
       <c r="R49" t="n">
-        <v>7045576</v>
+        <v>7045239</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6161,7 +6176,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6171,7 +6186,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6198,10 +6213,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123117683</v>
+        <v>123116920</v>
       </c>
       <c r="B50" t="n">
-        <v>78502</v>
+        <v>78150</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6214,21 +6229,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6238,13 +6253,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557966</v>
+        <v>557888</v>
       </c>
       <c r="R50" t="n">
-        <v>7045239</v>
+        <v>7045356</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6271,19 +6286,9 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6298,22 +6303,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123115068</v>
+        <v>123114009</v>
       </c>
       <c r="B51" t="n">
-        <v>92233</v>
+        <v>90917</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6326,21 +6331,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6350,10 +6355,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557961</v>
+        <v>558050</v>
       </c>
       <c r="R51" t="n">
-        <v>7045587</v>
+        <v>7045576</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6385,7 +6390,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6395,7 +6400,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6422,10 +6427,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123117651</v>
+        <v>123114354</v>
       </c>
       <c r="B52" t="n">
-        <v>57589</v>
+        <v>92233</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6438,43 +6443,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557907</v>
+        <v>557978</v>
       </c>
       <c r="R52" t="n">
-        <v>7045262</v>
+        <v>7045589</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,7 +6502,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6516,7 +6512,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6543,10 +6539,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123115166</v>
+        <v>123115087</v>
       </c>
       <c r="B53" t="n">
-        <v>78411</v>
+        <v>56688</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6555,38 +6551,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557961</v>
+        <v>557957</v>
       </c>
       <c r="R53" t="n">
-        <v>7045574</v>
+        <v>7045576</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6618,7 +6619,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6628,7 +6629,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6655,10 +6656,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123115087</v>
+        <v>123119791</v>
       </c>
       <c r="B54" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6667,31 +6668,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557957</v>
+        <v>557988</v>
       </c>
       <c r="R54" t="n">
-        <v>7045576</v>
+        <v>7045172</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6772,7 +6772,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123114354</v>
+        <v>123115068</v>
       </c>
       <c r="B55" t="n">
         <v>92233</v>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557978</v>
+        <v>557961</v>
       </c>
       <c r="R55" t="n">
-        <v>7045589</v>
+        <v>7045587</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122909459</v>
+        <v>122909181</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,31 +1499,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1532,10 +1536,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557966</v>
+        <v>558033</v>
       </c>
       <c r="R9" t="n">
-        <v>7045501</v>
+        <v>7045487</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122909181</v>
+        <v>122909459</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,35 +1620,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558033</v>
+        <v>557966</v>
       </c>
       <c r="R10" t="n">
-        <v>7045487</v>
+        <v>7045501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1703,7 +1698,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -4147,10 +4147,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122908738</v>
+        <v>122914666</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4163,34 +4163,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558014</v>
+        <v>557892</v>
       </c>
       <c r="R32" t="n">
-        <v>7045616</v>
+        <v>7045356</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4222,7 +4227,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4232,7 +4237,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4247,22 +4257,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122914666</v>
+        <v>122908738</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4275,39 +4285,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557892</v>
+        <v>558014</v>
       </c>
       <c r="R33" t="n">
-        <v>7045356</v>
+        <v>7045616</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4339,7 +4344,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4349,12 +4354,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4369,12 +4369,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5061,10 +5061,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122908146</v>
+        <v>122911743</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5073,42 +5073,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557988</v>
+        <v>558114</v>
       </c>
       <c r="R40" t="n">
-        <v>7045659</v>
+        <v>7045374</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5140,7 +5136,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5150,7 +5146,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5165,22 +5161,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122911743</v>
+        <v>122908146</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5189,38 +5185,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558114</v>
+        <v>557988</v>
       </c>
       <c r="R41" t="n">
-        <v>7045374</v>
+        <v>7045659</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5277,12 +5277,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5401,10 +5401,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122909723</v>
+        <v>122908497</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5413,38 +5413,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558113</v>
+        <v>557969</v>
       </c>
       <c r="R43" t="n">
-        <v>7045588</v>
+        <v>7045641</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5476,7 +5485,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5486,7 +5495,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5501,22 +5510,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122908497</v>
+        <v>122909723</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5525,47 +5534,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557969</v>
+        <v>558113</v>
       </c>
       <c r="R44" t="n">
-        <v>7045641</v>
+        <v>7045588</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5622,12 +5622,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883141</v>
+        <v>122882954</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +799,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557872</v>
+        <v>557874</v>
       </c>
       <c r="R3" t="n">
-        <v>7045237</v>
+        <v>7045270</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>+50 Ringhack på tall</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1021,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122885158</v>
+        <v>122883141</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,35 +1032,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557925</v>
+        <v>557872</v>
       </c>
       <c r="R5" t="n">
-        <v>7045226</v>
+        <v>7045237</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>+50 Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1366,7 +1366,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122882954</v>
+        <v>122885158</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557874</v>
+        <v>557925</v>
       </c>
       <c r="R8" t="n">
-        <v>7045270</v>
+        <v>7045226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122909181</v>
+        <v>122914531</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,47 +1499,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558033</v>
+        <v>557870</v>
       </c>
       <c r="R9" t="n">
-        <v>7045487</v>
+        <v>7045346</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122909459</v>
+        <v>122909523</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,43 +1611,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557966</v>
+        <v>558123</v>
       </c>
       <c r="R10" t="n">
-        <v>7045501</v>
+        <v>7045531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,12 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,22 +1703,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122914606</v>
+        <v>122909987</v>
       </c>
       <c r="B11" t="n">
-        <v>90972</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,34 +1731,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557893</v>
+        <v>558129</v>
       </c>
       <c r="R11" t="n">
-        <v>7045351</v>
+        <v>7045578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122909523</v>
+        <v>122909331</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,42 +1839,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558123</v>
+        <v>557986</v>
       </c>
       <c r="R12" t="n">
-        <v>7045531</v>
+        <v>7045500</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1921,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,22 +1932,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122914531</v>
+        <v>122908246</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,34 +1960,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557870</v>
+        <v>557977</v>
       </c>
       <c r="R13" t="n">
-        <v>7045346</v>
+        <v>7045628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2033,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122914405</v>
+        <v>122908377</v>
       </c>
       <c r="B14" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,38 +2072,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557976</v>
+        <v>557960</v>
       </c>
       <c r="R14" t="n">
-        <v>7045210</v>
+        <v>7045662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,22 +2160,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122910281</v>
+        <v>122914405</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,38 +2184,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558178</v>
+        <v>557976</v>
       </c>
       <c r="R15" t="n">
-        <v>7045498</v>
+        <v>7045210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,22 +2272,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122909331</v>
+        <v>122914868</v>
       </c>
       <c r="B16" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,39 +2300,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557986</v>
+        <v>557948</v>
       </c>
       <c r="R16" t="n">
-        <v>7045500</v>
+        <v>7045384</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,19 +2384,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908181</v>
+        <v>122908146</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2446,19 +2431,19 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557989</v>
+        <v>557988</v>
       </c>
       <c r="R17" t="n">
-        <v>7045623</v>
+        <v>7045659</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,7 +2512,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122913820</v>
+        <v>122914413</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2562,7 +2547,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2571,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558157</v>
+        <v>557884</v>
       </c>
       <c r="R18" t="n">
-        <v>7045329</v>
+        <v>7045302</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122909987</v>
+        <v>122909723</v>
       </c>
       <c r="B19" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,21 +2644,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2683,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558129</v>
+        <v>558113</v>
       </c>
       <c r="R19" t="n">
-        <v>7045578</v>
+        <v>7045588</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2713,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2755,10 +2740,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122912661</v>
+        <v>122908422</v>
       </c>
       <c r="B20" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2771,34 +2756,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558113</v>
+        <v>557977</v>
       </c>
       <c r="R20" t="n">
-        <v>7045372</v>
+        <v>7045673</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,7 +2830,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2867,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122908440</v>
+        <v>122910281</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2883,39 +2878,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557960</v>
+        <v>558178</v>
       </c>
       <c r="R21" t="n">
-        <v>7045650</v>
+        <v>7045498</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2947,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2957,12 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2977,22 +2962,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122908532</v>
+        <v>122909860</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,42 +2986,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557942</v>
+        <v>558133</v>
       </c>
       <c r="R22" t="n">
-        <v>7045683</v>
+        <v>7045474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3068,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3078,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3093,22 +3074,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122914573</v>
+        <v>122910006</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3121,21 +3102,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3145,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557892</v>
+        <v>558154</v>
       </c>
       <c r="R23" t="n">
-        <v>7045361</v>
+        <v>7045445</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3180,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3190,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,19 +3186,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122908779</v>
+        <v>122908181</v>
       </c>
       <c r="B24" t="n">
         <v>98365</v>
@@ -3252,7 +3233,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3261,10 +3242,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557996</v>
+        <v>557989</v>
       </c>
       <c r="R24" t="n">
-        <v>7045609</v>
+        <v>7045623</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3277,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3287,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,10 +3314,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122909860</v>
+        <v>122909459</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3349,34 +3330,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558133</v>
+        <v>557966</v>
       </c>
       <c r="R25" t="n">
-        <v>7045474</v>
+        <v>7045501</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3408,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3418,7 +3404,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3445,7 +3436,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122908666</v>
+        <v>122914573</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3481,14 +3472,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557951</v>
+        <v>557892</v>
       </c>
       <c r="R26" t="n">
-        <v>7045711</v>
+        <v>7045361</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3520,7 +3511,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,7 +3521,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3557,10 +3548,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122908422</v>
+        <v>122912661</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3573,39 +3564,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557977</v>
+        <v>558113</v>
       </c>
       <c r="R27" t="n">
-        <v>7045673</v>
+        <v>7045372</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3637,7 +3623,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3647,12 +3633,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3679,10 +3660,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122908559</v>
+        <v>122911743</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3695,39 +3676,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557959</v>
+        <v>558114</v>
       </c>
       <c r="R28" t="n">
-        <v>7045628</v>
+        <v>7045374</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3759,7 +3735,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3769,12 +3745,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3801,7 +3772,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122908377</v>
+        <v>122908447</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3841,10 +3812,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557960</v>
+        <v>557958</v>
       </c>
       <c r="R29" t="n">
-        <v>7045662</v>
+        <v>7045677</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3876,7 +3847,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3886,7 +3857,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3913,10 +3884,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122908038</v>
+        <v>122908779</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3925,43 +3896,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558017</v>
+        <v>557996</v>
       </c>
       <c r="R30" t="n">
-        <v>7045654</v>
+        <v>7045609</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3993,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4003,12 +3973,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4035,10 +4000,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122912795</v>
+        <v>122909181</v>
       </c>
       <c r="B31" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4047,38 +4012,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558128</v>
+        <v>558033</v>
       </c>
       <c r="R31" t="n">
-        <v>7045377</v>
+        <v>7045487</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4110,7 +4084,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4120,7 +4094,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4135,19 +4109,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122914666</v>
+        <v>122908038</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4183,19 +4157,19 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557892</v>
+        <v>558017</v>
       </c>
       <c r="R32" t="n">
-        <v>7045356</v>
+        <v>7045654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4227,7 +4201,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4237,12 +4211,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4269,10 +4243,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122908738</v>
+        <v>122914606</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>90972</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4285,21 +4259,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4309,10 +4283,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558014</v>
+        <v>557893</v>
       </c>
       <c r="R33" t="n">
-        <v>7045616</v>
+        <v>7045351</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4344,7 +4318,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4354,7 +4328,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4369,22 +4343,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122908246</v>
+        <v>122908532</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4393,42 +4367,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557977</v>
+        <v>557942</v>
       </c>
       <c r="R34" t="n">
-        <v>7045628</v>
+        <v>7045683</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4460,7 +4434,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4470,7 +4444,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4497,7 +4471,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910006</v>
+        <v>122908738</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4537,10 +4511,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558154</v>
+        <v>558014</v>
       </c>
       <c r="R35" t="n">
-        <v>7045445</v>
+        <v>7045616</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4572,7 +4546,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4582,7 +4556,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4609,10 +4583,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122914213</v>
+        <v>122914666</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4625,34 +4599,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557991</v>
+        <v>557892</v>
       </c>
       <c r="R36" t="n">
-        <v>7045335</v>
+        <v>7045356</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4684,7 +4663,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4694,7 +4673,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4721,7 +4705,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122914334</v>
+        <v>122914213</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4761,10 +4745,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557931</v>
+        <v>557991</v>
       </c>
       <c r="R37" t="n">
-        <v>7045323</v>
+        <v>7045335</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4796,7 +4780,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4806,7 +4790,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4833,10 +4817,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122914413</v>
+        <v>122908559</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4845,30 +4829,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4877,10 +4862,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557884</v>
+        <v>557959</v>
       </c>
       <c r="R38" t="n">
-        <v>7045302</v>
+        <v>7045628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4912,7 +4897,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4922,7 +4907,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4937,22 +4927,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122914868</v>
+        <v>122908497</v>
       </c>
       <c r="B39" t="n">
-        <v>79848</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4961,38 +4951,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557948</v>
+        <v>557969</v>
       </c>
       <c r="R39" t="n">
-        <v>7045384</v>
+        <v>7045641</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5024,7 +5023,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5034,7 +5033,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5049,22 +5048,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122911743</v>
+        <v>122908666</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5077,34 +5076,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558114</v>
+        <v>557951</v>
       </c>
       <c r="R40" t="n">
-        <v>7045374</v>
+        <v>7045711</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5136,7 +5135,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5146,7 +5145,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,19 +5160,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122908146</v>
+        <v>122913820</v>
       </c>
       <c r="B41" t="n">
         <v>98365</v>
@@ -5208,19 +5207,19 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557988</v>
+        <v>558157</v>
       </c>
       <c r="R41" t="n">
-        <v>7045659</v>
+        <v>7045329</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5252,7 +5251,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5262,7 +5261,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5289,7 +5288,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122914308</v>
+        <v>122914334</v>
       </c>
       <c r="B42" t="n">
         <v>78766</v>
@@ -5329,10 +5328,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557955</v>
+        <v>557931</v>
       </c>
       <c r="R42" t="n">
-        <v>7045351</v>
+        <v>7045323</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5364,7 +5363,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5374,7 +5373,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5401,10 +5400,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122908497</v>
+        <v>122914308</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5413,47 +5412,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557969</v>
+        <v>557955</v>
       </c>
       <c r="R43" t="n">
-        <v>7045641</v>
+        <v>7045351</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5485,7 +5475,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5495,7 +5485,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5510,22 +5500,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122909723</v>
+        <v>122909049</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5538,34 +5528,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558113</v>
+        <v>558048</v>
       </c>
       <c r="R44" t="n">
-        <v>7045588</v>
+        <v>7045527</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5597,7 +5592,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5607,7 +5602,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5622,22 +5622,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122908447</v>
+        <v>122912795</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5650,34 +5650,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557958</v>
+        <v>558128</v>
       </c>
       <c r="R45" t="n">
-        <v>7045677</v>
+        <v>7045377</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5746,7 +5746,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122909049</v>
+        <v>122908440</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5782,19 +5782,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558048</v>
+        <v>557960</v>
       </c>
       <c r="R46" t="n">
-        <v>7045527</v>
+        <v>7045650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5868,10 +5868,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123115166</v>
+        <v>123115068</v>
       </c>
       <c r="B47" t="n">
-        <v>78411</v>
+        <v>92233</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5880,25 +5880,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5911,7 +5911,7 @@
         <v>557961</v>
       </c>
       <c r="R47" t="n">
-        <v>7045574</v>
+        <v>7045587</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123117651</v>
+        <v>123117683</v>
       </c>
       <c r="B48" t="n">
-        <v>57589</v>
+        <v>78502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5992,47 +5992,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557907</v>
+        <v>557966</v>
       </c>
       <c r="R48" t="n">
-        <v>7045262</v>
+        <v>7045239</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6064,7 +6055,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6074,7 +6065,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6101,10 +6092,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123117683</v>
+        <v>123114009</v>
       </c>
       <c r="B49" t="n">
-        <v>78502</v>
+        <v>90917</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6113,25 +6104,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6141,10 +6132,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557966</v>
+        <v>558050</v>
       </c>
       <c r="R49" t="n">
-        <v>7045239</v>
+        <v>7045576</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6176,7 +6167,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6186,7 +6177,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6213,10 +6204,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123116920</v>
+        <v>123115166</v>
       </c>
       <c r="B50" t="n">
-        <v>78150</v>
+        <v>78411</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6229,21 +6220,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6253,13 +6244,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557888</v>
+        <v>557961</v>
       </c>
       <c r="R50" t="n">
-        <v>7045356</v>
+        <v>7045574</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6286,9 +6277,19 @@
           <t>2025-03-12</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6303,22 +6304,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123114009</v>
+        <v>123114354</v>
       </c>
       <c r="B51" t="n">
-        <v>90917</v>
+        <v>92233</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6331,21 +6332,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6355,10 +6356,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558050</v>
+        <v>557978</v>
       </c>
       <c r="R51" t="n">
-        <v>7045576</v>
+        <v>7045589</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6390,7 +6391,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6400,7 +6401,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6427,10 +6428,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123114354</v>
+        <v>123119791</v>
       </c>
       <c r="B52" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6439,38 +6440,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557978</v>
+        <v>557988</v>
       </c>
       <c r="R52" t="n">
-        <v>7045589</v>
+        <v>7045172</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6502,7 +6507,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6512,7 +6517,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6539,10 +6544,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123115087</v>
+        <v>123116920</v>
       </c>
       <c r="B53" t="n">
-        <v>56688</v>
+        <v>78150</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6551,46 +6556,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557957</v>
+        <v>557888</v>
       </c>
       <c r="R53" t="n">
-        <v>7045576</v>
+        <v>7045356</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6617,19 +6617,9 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6644,22 +6634,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123119791</v>
+        <v>123115087</v>
       </c>
       <c r="B54" t="n">
-        <v>98365</v>
+        <v>56688</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6668,30 +6658,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6700,10 +6691,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557988</v>
+        <v>557957</v>
       </c>
       <c r="R54" t="n">
-        <v>7045172</v>
+        <v>7045576</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6735,7 +6726,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6745,7 +6736,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6772,10 +6763,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123115068</v>
+        <v>123117651</v>
       </c>
       <c r="B55" t="n">
-        <v>92233</v>
+        <v>57589</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6788,34 +6779,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557961</v>
+        <v>557907</v>
       </c>
       <c r="R55" t="n">
-        <v>7045587</v>
+        <v>7045262</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -2862,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122910281</v>
+        <v>122909860</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,34 +2878,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558178</v>
+        <v>558133</v>
       </c>
       <c r="R21" t="n">
-        <v>7045498</v>
+        <v>7045474</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,22 +2962,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122909860</v>
+        <v>122910281</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,34 +2990,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558133</v>
+        <v>558178</v>
       </c>
       <c r="R22" t="n">
-        <v>7045474</v>
+        <v>7045498</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,12 +3074,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4817,10 +4817,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122908559</v>
+        <v>122908497</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4829,43 +4829,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557959</v>
+        <v>557969</v>
       </c>
       <c r="R38" t="n">
-        <v>7045628</v>
+        <v>7045641</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4897,7 +4901,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4907,12 +4911,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4939,10 +4938,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122908497</v>
+        <v>122908559</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4951,47 +4950,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557969</v>
+        <v>557959</v>
       </c>
       <c r="R39" t="n">
-        <v>7045641</v>
+        <v>7045628</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5023,7 +5018,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5033,7 +5028,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5060,10 +5060,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122908666</v>
+        <v>122913820</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5072,38 +5072,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557951</v>
+        <v>558157</v>
       </c>
       <c r="R40" t="n">
-        <v>7045711</v>
+        <v>7045329</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5135,7 +5139,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5145,7 +5149,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5172,10 +5176,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122913820</v>
+        <v>122908666</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5184,42 +5188,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558157</v>
+        <v>557951</v>
       </c>
       <c r="R41" t="n">
-        <v>7045329</v>
+        <v>7045711</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6204,10 +6204,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123115166</v>
+        <v>123119791</v>
       </c>
       <c r="B50" t="n">
-        <v>78411</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6216,38 +6216,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557961</v>
+        <v>557988</v>
       </c>
       <c r="R50" t="n">
-        <v>7045574</v>
+        <v>7045172</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6279,7 +6283,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6289,7 +6293,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6428,10 +6432,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123119791</v>
+        <v>123115166</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>78411</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6440,42 +6444,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557988</v>
+        <v>557961</v>
       </c>
       <c r="R52" t="n">
-        <v>7045172</v>
+        <v>7045574</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -1254,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122883501</v>
+        <v>122885158</v>
       </c>
       <c r="B7" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,38 +1266,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557908</v>
+        <v>557925</v>
       </c>
       <c r="R7" t="n">
-        <v>7045230</v>
+        <v>7045226</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122885158</v>
+        <v>122883501</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,47 +1387,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557925</v>
+        <v>557908</v>
       </c>
       <c r="R8" t="n">
-        <v>7045226</v>
+        <v>7045230</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122914531</v>
+        <v>122909523</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,38 +1499,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557870</v>
+        <v>558123</v>
       </c>
       <c r="R9" t="n">
-        <v>7045346</v>
+        <v>7045531</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1566,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1576,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1603,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122909523</v>
+        <v>122914531</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,42 +1615,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558123</v>
+        <v>557870</v>
       </c>
       <c r="R10" t="n">
-        <v>7045531</v>
+        <v>7045346</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2862,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122909860</v>
+        <v>122910281</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,34 +2878,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558133</v>
+        <v>558178</v>
       </c>
       <c r="R21" t="n">
-        <v>7045474</v>
+        <v>7045498</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,22 +2962,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122910281</v>
+        <v>122909860</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,34 +2990,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558178</v>
+        <v>558133</v>
       </c>
       <c r="R22" t="n">
-        <v>7045498</v>
+        <v>7045474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,12 +3074,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -4471,10 +4471,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122908738</v>
+        <v>122914666</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4487,34 +4487,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558014</v>
+        <v>557892</v>
       </c>
       <c r="R35" t="n">
-        <v>7045616</v>
+        <v>7045356</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4546,7 +4551,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4556,7 +4561,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4571,22 +4581,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122914666</v>
+        <v>122914213</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4599,39 +4609,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557892</v>
+        <v>557991</v>
       </c>
       <c r="R36" t="n">
-        <v>7045356</v>
+        <v>7045335</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4663,7 +4668,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4673,12 +4678,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4705,10 +4705,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122914213</v>
+        <v>122908738</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4721,21 +4721,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557991</v>
+        <v>558014</v>
       </c>
       <c r="R37" t="n">
-        <v>7045335</v>
+        <v>7045616</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4805,22 +4805,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122908497</v>
+        <v>122908559</v>
       </c>
       <c r="B38" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4829,47 +4829,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557969</v>
+        <v>557959</v>
       </c>
       <c r="R38" t="n">
-        <v>7045641</v>
+        <v>7045628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4901,7 +4897,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4911,7 +4907,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4938,10 +4939,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122908559</v>
+        <v>122908497</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4950,43 +4951,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557959</v>
+        <v>557969</v>
       </c>
       <c r="R39" t="n">
-        <v>7045628</v>
+        <v>7045641</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5018,7 +5023,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5028,12 +5033,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5060,10 +5060,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122913820</v>
+        <v>122908666</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5072,42 +5072,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558157</v>
+        <v>557951</v>
       </c>
       <c r="R40" t="n">
-        <v>7045329</v>
+        <v>7045711</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5139,7 +5135,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5149,7 +5145,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5176,10 +5172,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122908666</v>
+        <v>122913820</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5188,38 +5184,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557951</v>
+        <v>558157</v>
       </c>
       <c r="R41" t="n">
-        <v>7045711</v>
+        <v>7045329</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122887288</v>
+        <v>122887408</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558116</v>
+        <v>558107</v>
       </c>
       <c r="R2" t="n">
-        <v>7045369</v>
+        <v>7045485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122882954</v>
+        <v>122887288</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557874</v>
+        <v>558116</v>
       </c>
       <c r="R3" t="n">
-        <v>7045270</v>
+        <v>7045369</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122887408</v>
+        <v>122885158</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558107</v>
+        <v>557925</v>
       </c>
       <c r="R4" t="n">
-        <v>7045485</v>
+        <v>7045226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883141</v>
+        <v>122883501</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>92233</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,43 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557872</v>
+        <v>557908</v>
       </c>
       <c r="R5" t="n">
-        <v>7045237</v>
+        <v>7045230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>+50 Ringhack på tall</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122887465</v>
+        <v>122882954</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,38 +1144,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558046</v>
+        <v>557874</v>
       </c>
       <c r="R6" t="n">
-        <v>7045577</v>
+        <v>7045270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122885158</v>
+        <v>122887465</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,47 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557925</v>
+        <v>558046</v>
       </c>
       <c r="R7" t="n">
-        <v>7045226</v>
+        <v>7045577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122883501</v>
+        <v>122883141</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,38 +1377,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557908</v>
+        <v>557872</v>
       </c>
       <c r="R8" t="n">
-        <v>7045230</v>
+        <v>7045237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1455,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>+50 Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122909523</v>
+        <v>122908447</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,42 +1499,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558123</v>
+        <v>557958</v>
       </c>
       <c r="R9" t="n">
-        <v>7045531</v>
+        <v>7045677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1576,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122914531</v>
+        <v>122908779</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,38 +1611,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557870</v>
+        <v>557996</v>
       </c>
       <c r="R10" t="n">
-        <v>7045346</v>
+        <v>7045609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122909987</v>
+        <v>122909181</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,38 +1727,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558129</v>
+        <v>558033</v>
       </c>
       <c r="R11" t="n">
-        <v>7045578</v>
+        <v>7045487</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,22 +1824,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122909331</v>
+        <v>122909459</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,16 +1852,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1872,10 +1881,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557986</v>
+        <v>557966</v>
       </c>
       <c r="R12" t="n">
-        <v>7045500</v>
+        <v>7045501</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1916,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1926,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122908246</v>
+        <v>122909860</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,38 +1974,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557977</v>
+        <v>558133</v>
       </c>
       <c r="R13" t="n">
-        <v>7045628</v>
+        <v>7045474</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,7 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,22 +2058,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122908377</v>
+        <v>122908422</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,34 +2086,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557960</v>
+        <v>557977</v>
       </c>
       <c r="R14" t="n">
-        <v>7045662</v>
+        <v>7045673</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2160,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122914405</v>
+        <v>122914413</v>
       </c>
       <c r="B15" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,38 +2204,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557976</v>
+        <v>557884</v>
       </c>
       <c r="R15" t="n">
-        <v>7045210</v>
+        <v>7045302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2281,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,22 +2296,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122914868</v>
+        <v>122908377</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,34 +2324,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557948</v>
+        <v>557960</v>
       </c>
       <c r="R16" t="n">
-        <v>7045384</v>
+        <v>7045662</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908146</v>
+        <v>122908738</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,42 +2432,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557988</v>
+        <v>558014</v>
       </c>
       <c r="R17" t="n">
-        <v>7045659</v>
+        <v>7045616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,22 +2520,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122914413</v>
+        <v>122914405</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,42 +2544,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557884</v>
+        <v>557976</v>
       </c>
       <c r="R18" t="n">
-        <v>7045302</v>
+        <v>7045210</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2601,7 +2617,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,22 +2632,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122909723</v>
+        <v>122911743</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2644,34 +2660,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558113</v>
+        <v>558114</v>
       </c>
       <c r="R19" t="n">
-        <v>7045588</v>
+        <v>7045374</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2703,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,7 +2729,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,22 +2744,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122908422</v>
+        <v>122908666</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,39 +2772,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557977</v>
+        <v>557951</v>
       </c>
       <c r="R20" t="n">
-        <v>7045673</v>
+        <v>7045711</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2820,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2830,12 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122910281</v>
+        <v>122909049</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2878,34 +2884,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558178</v>
+        <v>558048</v>
       </c>
       <c r="R21" t="n">
-        <v>7045498</v>
+        <v>7045527</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2958,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,22 +2978,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122909860</v>
+        <v>122908497</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,38 +3002,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558133</v>
+        <v>557969</v>
       </c>
       <c r="R22" t="n">
-        <v>7045474</v>
+        <v>7045641</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3111,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122910006</v>
+        <v>122908532</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3098,38 +3123,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558154</v>
+        <v>557942</v>
       </c>
       <c r="R23" t="n">
-        <v>7045445</v>
+        <v>7045683</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3161,7 +3190,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3200,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3186,22 +3215,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122908181</v>
+        <v>122914308</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3210,42 +3239,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557989</v>
+        <v>557955</v>
       </c>
       <c r="R24" t="n">
-        <v>7045623</v>
+        <v>7045351</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3277,7 +3302,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3287,7 +3312,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3314,7 +3339,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122909459</v>
+        <v>122908246</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3347,10 +3372,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3359,10 +3383,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557966</v>
+        <v>557977</v>
       </c>
       <c r="R25" t="n">
-        <v>7045501</v>
+        <v>7045628</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3418,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,12 +3428,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,22 +3443,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122914573</v>
+        <v>122914868</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3452,21 +3471,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3476,10 +3495,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557892</v>
+        <v>557948</v>
       </c>
       <c r="R26" t="n">
-        <v>7045361</v>
+        <v>7045384</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3511,7 +3530,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3521,7 +3540,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3548,10 +3567,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122912661</v>
+        <v>122914213</v>
       </c>
       <c r="B27" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3564,21 +3583,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3588,10 +3607,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558113</v>
+        <v>557991</v>
       </c>
       <c r="R27" t="n">
-        <v>7045372</v>
+        <v>7045335</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3623,7 +3642,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3633,7 +3652,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3660,10 +3679,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122911743</v>
+        <v>122908440</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3676,34 +3695,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558114</v>
+        <v>557960</v>
       </c>
       <c r="R28" t="n">
-        <v>7045374</v>
+        <v>7045650</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3735,7 +3759,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3745,7 +3769,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3772,7 +3801,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122908447</v>
+        <v>122914531</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3808,14 +3837,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557958</v>
+        <v>557870</v>
       </c>
       <c r="R29" t="n">
-        <v>7045677</v>
+        <v>7045346</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3847,7 +3876,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3857,7 +3886,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,10 +3913,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122908779</v>
+        <v>122910006</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,42 +3925,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557996</v>
+        <v>558154</v>
       </c>
       <c r="R30" t="n">
-        <v>7045609</v>
+        <v>7045445</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3963,7 +3988,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,7 +3998,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3988,22 +4013,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122909181</v>
+        <v>122908559</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4012,35 +4037,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4049,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558033</v>
+        <v>557959</v>
       </c>
       <c r="R31" t="n">
-        <v>7045487</v>
+        <v>7045628</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4084,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4094,7 +4115,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4121,10 +4147,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122908038</v>
+        <v>122912661</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4137,39 +4163,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558017</v>
+        <v>558113</v>
       </c>
       <c r="R32" t="n">
-        <v>7045654</v>
+        <v>7045372</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4201,7 +4222,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4211,12 +4232,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4243,10 +4259,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122914606</v>
+        <v>122909523</v>
       </c>
       <c r="B33" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4255,38 +4271,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557893</v>
+        <v>558123</v>
       </c>
       <c r="R33" t="n">
-        <v>7045351</v>
+        <v>7045531</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4318,7 +4338,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4328,7 +4348,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4355,10 +4375,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122908532</v>
+        <v>122914666</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4367,42 +4387,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557942</v>
+        <v>557892</v>
       </c>
       <c r="R34" t="n">
-        <v>7045683</v>
+        <v>7045356</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4434,7 +4455,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4444,7 +4465,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4471,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122914666</v>
+        <v>122910281</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4487,39 +4513,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557892</v>
+        <v>558178</v>
       </c>
       <c r="R35" t="n">
-        <v>7045356</v>
+        <v>7045498</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4551,7 +4572,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4561,12 +4582,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4593,7 +4609,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122914213</v>
+        <v>122909723</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4629,14 +4645,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557991</v>
+        <v>558113</v>
       </c>
       <c r="R36" t="n">
-        <v>7045335</v>
+        <v>7045588</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4668,7 +4684,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4678,7 +4694,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4705,10 +4721,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122908738</v>
+        <v>122914573</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4721,21 +4737,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4745,10 +4761,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558014</v>
+        <v>557892</v>
       </c>
       <c r="R37" t="n">
-        <v>7045616</v>
+        <v>7045361</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4780,7 +4796,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4790,7 +4806,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4805,22 +4821,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122908559</v>
+        <v>122909987</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4833,39 +4849,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557959</v>
+        <v>558129</v>
       </c>
       <c r="R38" t="n">
-        <v>7045628</v>
+        <v>7045578</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4897,7 +4908,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4907,12 +4918,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4927,19 +4933,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122908497</v>
+        <v>122908181</v>
       </c>
       <c r="B39" t="n">
         <v>98365</v>
@@ -4974,24 +4980,19 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557969</v>
+        <v>557989</v>
       </c>
       <c r="R39" t="n">
-        <v>7045641</v>
+        <v>7045623</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5023,7 +5024,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5033,7 +5034,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5048,22 +5049,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122908666</v>
+        <v>122912795</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>82553</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5076,34 +5077,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557951</v>
+        <v>558128</v>
       </c>
       <c r="R40" t="n">
-        <v>7045711</v>
+        <v>7045377</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5135,7 +5136,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5145,7 +5146,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5172,10 +5173,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122913820</v>
+        <v>122914334</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5184,42 +5185,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558157</v>
+        <v>557931</v>
       </c>
       <c r="R41" t="n">
-        <v>7045329</v>
+        <v>7045323</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5251,7 +5248,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5261,7 +5258,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5288,10 +5285,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122914334</v>
+        <v>122914606</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>90972</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5304,21 +5301,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5328,10 +5325,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557931</v>
+        <v>557893</v>
       </c>
       <c r="R42" t="n">
-        <v>7045323</v>
+        <v>7045351</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5363,7 +5360,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5373,7 +5370,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5400,10 +5397,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122914308</v>
+        <v>122913820</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5412,38 +5409,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557955</v>
+        <v>558157</v>
       </c>
       <c r="R43" t="n">
-        <v>7045351</v>
+        <v>7045329</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5475,7 +5476,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5485,7 +5486,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5512,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122909049</v>
+        <v>122908146</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5524,43 +5525,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558048</v>
+        <v>557988</v>
       </c>
       <c r="R44" t="n">
-        <v>7045527</v>
+        <v>7045659</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5602,12 +5602,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5622,22 +5617,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122912795</v>
+        <v>122909331</v>
       </c>
       <c r="B45" t="n">
-        <v>82553</v>
+        <v>57494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5650,34 +5645,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558128</v>
+        <v>557986</v>
       </c>
       <c r="R45" t="n">
-        <v>7045377</v>
+        <v>7045500</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5734,19 +5734,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122908440</v>
+        <v>122908038</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557960</v>
+        <v>558017</v>
       </c>
       <c r="R46" t="n">
-        <v>7045650</v>
+        <v>7045654</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5856,22 +5856,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123115068</v>
+        <v>123117683</v>
       </c>
       <c r="B47" t="n">
-        <v>92233</v>
+        <v>78502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5880,25 +5880,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557961</v>
+        <v>557966</v>
       </c>
       <c r="R47" t="n">
-        <v>7045587</v>
+        <v>7045239</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123117683</v>
+        <v>123116920</v>
       </c>
       <c r="B48" t="n">
-        <v>78502</v>
+        <v>78150</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5996,21 +5996,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557966</v>
+        <v>557888</v>
       </c>
       <c r="R48" t="n">
-        <v>7045239</v>
+        <v>7045356</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6053,19 +6053,9 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6080,22 +6070,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123114009</v>
+        <v>123119791</v>
       </c>
       <c r="B49" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6104,38 +6094,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558050</v>
+        <v>557988</v>
       </c>
       <c r="R49" t="n">
-        <v>7045576</v>
+        <v>7045172</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6167,7 +6161,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6177,7 +6171,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,10 +6198,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123119791</v>
+        <v>123114354</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6216,42 +6210,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557988</v>
+        <v>557978</v>
       </c>
       <c r="R50" t="n">
-        <v>7045172</v>
+        <v>7045589</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6283,7 +6273,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6293,7 +6283,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6320,10 +6310,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123114354</v>
+        <v>123115087</v>
       </c>
       <c r="B51" t="n">
-        <v>92233</v>
+        <v>56688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6336,34 +6326,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557978</v>
+        <v>557957</v>
       </c>
       <c r="R51" t="n">
-        <v>7045589</v>
+        <v>7045576</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6395,7 +6390,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6405,7 +6400,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6432,10 +6427,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123115166</v>
+        <v>123117651</v>
       </c>
       <c r="B52" t="n">
-        <v>78411</v>
+        <v>57589</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6444,38 +6439,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557961</v>
+        <v>557907</v>
       </c>
       <c r="R52" t="n">
-        <v>7045574</v>
+        <v>7045262</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6507,7 +6511,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6517,7 +6521,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6544,10 +6548,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123116920</v>
+        <v>123115166</v>
       </c>
       <c r="B53" t="n">
-        <v>78150</v>
+        <v>78411</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6560,21 +6564,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6584,13 +6588,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557888</v>
+        <v>557961</v>
       </c>
       <c r="R53" t="n">
-        <v>7045356</v>
+        <v>7045574</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6617,9 +6621,19 @@
           <t>2025-03-12</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6634,22 +6648,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123115087</v>
+        <v>123115068</v>
       </c>
       <c r="B54" t="n">
-        <v>56688</v>
+        <v>92233</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6662,39 +6676,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557957</v>
+        <v>557961</v>
       </c>
       <c r="R54" t="n">
-        <v>7045576</v>
+        <v>7045587</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6726,7 +6735,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6736,7 +6745,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6763,10 +6772,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123117651</v>
+        <v>123114009</v>
       </c>
       <c r="B55" t="n">
-        <v>57589</v>
+        <v>90917</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6779,43 +6788,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557907</v>
+        <v>558050</v>
       </c>
       <c r="R55" t="n">
-        <v>7045262</v>
+        <v>7045576</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122887408</v>
+        <v>122883501</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558107</v>
+        <v>557908</v>
       </c>
       <c r="R2" t="n">
-        <v>7045485</v>
+        <v>7045230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122887288</v>
+        <v>122885158</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558116</v>
+        <v>557925</v>
       </c>
       <c r="R3" t="n">
-        <v>7045369</v>
+        <v>7045226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122885158</v>
+        <v>122883141</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +920,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -948,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557925</v>
+        <v>557872</v>
       </c>
       <c r="R4" t="n">
-        <v>7045226</v>
+        <v>7045237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>+50 Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883501</v>
+        <v>122887465</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1042,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557908</v>
+        <v>558046</v>
       </c>
       <c r="R5" t="n">
-        <v>7045230</v>
+        <v>7045577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1253,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122887465</v>
+        <v>122887288</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1279,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558046</v>
+        <v>558116</v>
       </c>
       <c r="R7" t="n">
-        <v>7045577</v>
+        <v>7045369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122883141</v>
+        <v>122887408</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,39 +1391,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557872</v>
+        <v>558107</v>
       </c>
       <c r="R8" t="n">
-        <v>7045237</v>
+        <v>7045485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,12 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>+50 Ringhack på tall</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,7 +1487,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122908447</v>
+        <v>122914573</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1523,14 +1523,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557958</v>
+        <v>557892</v>
       </c>
       <c r="R9" t="n">
-        <v>7045677</v>
+        <v>7045361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122908779</v>
+        <v>122908738</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,42 +1611,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557996</v>
+        <v>558014</v>
       </c>
       <c r="R10" t="n">
-        <v>7045609</v>
+        <v>7045616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,22 +1699,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122909181</v>
+        <v>122911743</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,47 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558033</v>
+        <v>558114</v>
       </c>
       <c r="R11" t="n">
-        <v>7045487</v>
+        <v>7045374</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122909459</v>
+        <v>122909860</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,39 +1839,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557966</v>
+        <v>558133</v>
       </c>
       <c r="R12" t="n">
-        <v>7045501</v>
+        <v>7045474</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1926,12 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122909860</v>
+        <v>122909459</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,34 +1951,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558133</v>
+        <v>557966</v>
       </c>
       <c r="R13" t="n">
-        <v>7045474</v>
+        <v>7045501</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2025,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2192,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122914413</v>
+        <v>122914405</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,42 +2191,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557884</v>
+        <v>557976</v>
       </c>
       <c r="R15" t="n">
-        <v>7045302</v>
+        <v>7045210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2271,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,22 +2279,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122908377</v>
+        <v>122908559</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,34 +2307,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557960</v>
+        <v>557959</v>
       </c>
       <c r="R16" t="n">
-        <v>7045662</v>
+        <v>7045628</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2381,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,22 +2401,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908738</v>
+        <v>122914413</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,38 +2425,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558014</v>
+        <v>557884</v>
       </c>
       <c r="R17" t="n">
-        <v>7045616</v>
+        <v>7045302</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,7 +2492,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2502,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,22 +2517,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122914405</v>
+        <v>122910281</v>
       </c>
       <c r="B18" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,38 +2541,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557976</v>
+        <v>558178</v>
       </c>
       <c r="R18" t="n">
-        <v>7045210</v>
+        <v>7045498</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2607,7 +2604,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,7 +2614,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,22 +2629,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122911743</v>
+        <v>122914531</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,21 +2657,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2684,10 +2681,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558114</v>
+        <v>557870</v>
       </c>
       <c r="R19" t="n">
-        <v>7045374</v>
+        <v>7045346</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2719,7 +2716,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2726,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,22 +2741,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122908666</v>
+        <v>122914606</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>90972</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,34 +2769,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557951</v>
+        <v>557893</v>
       </c>
       <c r="R20" t="n">
-        <v>7045711</v>
+        <v>7045351</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122909049</v>
+        <v>122912661</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>82553</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,39 +2881,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558048</v>
+        <v>558113</v>
       </c>
       <c r="R21" t="n">
-        <v>7045527</v>
+        <v>7045372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,12 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,19 +2965,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122908497</v>
+        <v>122908146</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -3025,12 +3012,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3039,10 +3021,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557969</v>
+        <v>557988</v>
       </c>
       <c r="R22" t="n">
-        <v>7045641</v>
+        <v>7045659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3056,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3066,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,22 +3081,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122908532</v>
+        <v>122909987</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,42 +3105,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557942</v>
+        <v>558129</v>
       </c>
       <c r="R23" t="n">
-        <v>7045683</v>
+        <v>7045578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3190,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3200,7 +3178,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3227,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122914308</v>
+        <v>122908181</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3239,38 +3217,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557955</v>
+        <v>557989</v>
       </c>
       <c r="R24" t="n">
-        <v>7045351</v>
+        <v>7045623</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3302,7 +3284,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3312,7 +3294,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3339,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122908246</v>
+        <v>122908532</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3351,42 +3333,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557977</v>
+        <v>557942</v>
       </c>
       <c r="R25" t="n">
-        <v>7045628</v>
+        <v>7045683</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3418,7 +3400,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3428,7 +3410,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3455,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122914868</v>
+        <v>122908440</v>
       </c>
       <c r="B26" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3471,34 +3453,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557948</v>
+        <v>557960</v>
       </c>
       <c r="R26" t="n">
-        <v>7045384</v>
+        <v>7045650</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3530,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3540,7 +3527,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3555,12 +3547,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3679,10 +3671,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122908440</v>
+        <v>122909331</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3695,16 +3687,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3720,14 +3712,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557960</v>
+        <v>557986</v>
       </c>
       <c r="R28" t="n">
-        <v>7045650</v>
+        <v>7045500</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3759,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3769,12 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3801,10 +3788,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122914531</v>
+        <v>122908038</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3817,34 +3804,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557870</v>
+        <v>558017</v>
       </c>
       <c r="R29" t="n">
-        <v>7045346</v>
+        <v>7045654</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3876,7 +3868,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3886,7 +3878,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3913,10 +3910,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122910006</v>
+        <v>122914308</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3929,21 +3926,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3953,10 +3950,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558154</v>
+        <v>557955</v>
       </c>
       <c r="R30" t="n">
-        <v>7045445</v>
+        <v>7045351</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3988,7 +3985,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,7 +3995,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,22 +4010,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122908559</v>
+        <v>122908779</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4037,31 +4034,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4070,10 +4066,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557959</v>
+        <v>557996</v>
       </c>
       <c r="R31" t="n">
-        <v>7045628</v>
+        <v>7045609</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4105,7 +4101,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,12 +4111,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4135,22 +4126,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122912661</v>
+        <v>122909523</v>
       </c>
       <c r="B32" t="n">
-        <v>82553</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4159,38 +4150,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558113</v>
+        <v>558123</v>
       </c>
       <c r="R32" t="n">
-        <v>7045372</v>
+        <v>7045531</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4222,7 +4217,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4232,7 +4227,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4259,7 +4254,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122909523</v>
+        <v>122913820</v>
       </c>
       <c r="B33" t="n">
         <v>98365</v>
@@ -4294,19 +4289,19 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558123</v>
+        <v>558157</v>
       </c>
       <c r="R33" t="n">
-        <v>7045531</v>
+        <v>7045329</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4338,7 +4333,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4348,7 +4343,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4375,10 +4370,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122914666</v>
+        <v>122908377</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4391,39 +4386,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557892</v>
+        <v>557960</v>
       </c>
       <c r="R34" t="n">
-        <v>7045356</v>
+        <v>7045662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4455,7 +4445,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4465,12 +4455,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4497,10 +4482,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910281</v>
+        <v>122910006</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4513,34 +4498,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558178</v>
+        <v>558154</v>
       </c>
       <c r="R35" t="n">
-        <v>7045498</v>
+        <v>7045445</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4572,7 +4557,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4582,7 +4567,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4597,19 +4582,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122909723</v>
+        <v>122908666</v>
       </c>
       <c r="B36" t="n">
         <v>78766</v>
@@ -4645,14 +4630,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558113</v>
+        <v>557951</v>
       </c>
       <c r="R36" t="n">
-        <v>7045588</v>
+        <v>7045711</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4684,7 +4669,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4694,7 +4679,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4721,7 +4706,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122914573</v>
+        <v>122914334</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4761,10 +4746,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557892</v>
+        <v>557931</v>
       </c>
       <c r="R37" t="n">
-        <v>7045361</v>
+        <v>7045323</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4796,7 +4781,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4806,7 +4791,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4833,10 +4818,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122909987</v>
+        <v>122908447</v>
       </c>
       <c r="B38" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4849,34 +4834,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558129</v>
+        <v>557958</v>
       </c>
       <c r="R38" t="n">
-        <v>7045578</v>
+        <v>7045677</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4908,7 +4893,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4918,7 +4903,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4945,10 +4930,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122908181</v>
+        <v>122909049</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4957,30 +4942,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4989,10 +4975,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557989</v>
+        <v>558048</v>
       </c>
       <c r="R39" t="n">
-        <v>7045623</v>
+        <v>7045527</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5024,7 +5010,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5034,7 +5020,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5049,22 +5040,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122912795</v>
+        <v>122908246</v>
       </c>
       <c r="B40" t="n">
-        <v>82553</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5077,34 +5068,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558128</v>
+        <v>557977</v>
       </c>
       <c r="R40" t="n">
-        <v>7045377</v>
+        <v>7045628</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5136,7 +5131,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5146,7 +5141,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5173,10 +5168,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122914334</v>
+        <v>122908497</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5185,38 +5180,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557931</v>
+        <v>557969</v>
       </c>
       <c r="R41" t="n">
-        <v>7045323</v>
+        <v>7045641</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5248,7 +5252,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5258,7 +5262,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5273,22 +5277,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122914606</v>
+        <v>122909723</v>
       </c>
       <c r="B42" t="n">
-        <v>90972</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5301,34 +5305,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557893</v>
+        <v>558113</v>
       </c>
       <c r="R42" t="n">
-        <v>7045351</v>
+        <v>7045588</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5360,7 +5364,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5370,7 +5374,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5397,10 +5401,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122913820</v>
+        <v>122912795</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>82553</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5409,42 +5413,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558157</v>
+        <v>558128</v>
       </c>
       <c r="R43" t="n">
-        <v>7045329</v>
+        <v>7045377</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5513,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122908146</v>
+        <v>122914868</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>79848</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5525,42 +5525,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557988</v>
+        <v>557948</v>
       </c>
       <c r="R44" t="n">
-        <v>7045659</v>
+        <v>7045384</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5592,7 +5588,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5602,7 +5598,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5629,10 +5625,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122909331</v>
+        <v>122914666</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5645,16 +5641,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5665,7 +5661,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5674,10 +5670,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557986</v>
+        <v>557892</v>
       </c>
       <c r="R45" t="n">
-        <v>7045500</v>
+        <v>7045356</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5709,7 +5705,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5719,7 +5715,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5734,22 +5735,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122908038</v>
+        <v>122909181</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5758,43 +5759,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558017</v>
+        <v>558033</v>
       </c>
       <c r="R46" t="n">
-        <v>7045654</v>
+        <v>7045487</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5826,7 +5831,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5836,12 +5841,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5856,22 +5856,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123117683</v>
+        <v>123114009</v>
       </c>
       <c r="B47" t="n">
-        <v>78502</v>
+        <v>90917</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5880,25 +5880,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557966</v>
+        <v>558050</v>
       </c>
       <c r="R47" t="n">
-        <v>7045239</v>
+        <v>7045576</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5980,10 +5980,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123116920</v>
+        <v>123117683</v>
       </c>
       <c r="B48" t="n">
-        <v>78150</v>
+        <v>78502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5996,21 +5996,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557888</v>
+        <v>557966</v>
       </c>
       <c r="R48" t="n">
-        <v>7045356</v>
+        <v>7045239</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6053,9 +6053,19 @@
           <t>2025-03-12</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6070,22 +6080,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123119791</v>
+        <v>123114354</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6094,42 +6104,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557988</v>
+        <v>557978</v>
       </c>
       <c r="R49" t="n">
-        <v>7045172</v>
+        <v>7045589</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6161,7 +6167,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6171,7 +6177,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6198,10 +6204,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123114354</v>
+        <v>123116920</v>
       </c>
       <c r="B50" t="n">
-        <v>92233</v>
+        <v>78150</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6210,25 +6216,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6238,13 +6244,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557978</v>
+        <v>557888</v>
       </c>
       <c r="R50" t="n">
-        <v>7045589</v>
+        <v>7045356</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6271,19 +6277,9 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6298,22 +6294,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123115087</v>
+        <v>123117651</v>
       </c>
       <c r="B51" t="n">
-        <v>56688</v>
+        <v>57589</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6326,27 +6322,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557957</v>
+        <v>557907</v>
       </c>
       <c r="R51" t="n">
-        <v>7045576</v>
+        <v>7045262</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6427,10 +6427,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123117651</v>
+        <v>123119791</v>
       </c>
       <c r="B52" t="n">
-        <v>57589</v>
+        <v>98365</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6439,35 +6439,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6476,10 +6471,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557907</v>
+        <v>557988</v>
       </c>
       <c r="R52" t="n">
-        <v>7045262</v>
+        <v>7045172</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6511,7 +6506,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6521,7 +6516,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6772,10 +6767,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123114009</v>
+        <v>123115087</v>
       </c>
       <c r="B55" t="n">
-        <v>90917</v>
+        <v>56688</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6788,31 +6783,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558050</v>
+        <v>557957</v>
       </c>
       <c r="R55" t="n">
         <v>7045576</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122908181</v>
+        <v>122908440</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3217,42 +3217,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557989</v>
+        <v>557960</v>
       </c>
       <c r="R24" t="n">
-        <v>7045623</v>
+        <v>7045650</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3294,7 +3295,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,19 +3315,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122908532</v>
+        <v>122908181</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3356,19 +3362,19 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557942</v>
+        <v>557989</v>
       </c>
       <c r="R25" t="n">
-        <v>7045683</v>
+        <v>7045623</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3400,7 +3406,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3410,7 +3416,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3437,10 +3443,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122908440</v>
+        <v>122908532</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3449,31 +3455,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3482,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557960</v>
+        <v>557942</v>
       </c>
       <c r="R26" t="n">
-        <v>7045650</v>
+        <v>7045683</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,7 +3522,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3527,12 +3532,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,12 +3547,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -3205,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122908440</v>
+        <v>122908181</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3217,43 +3217,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557960</v>
+        <v>557989</v>
       </c>
       <c r="R24" t="n">
-        <v>7045650</v>
+        <v>7045623</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3285,7 +3284,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3295,12 +3294,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,19 +3309,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122908181</v>
+        <v>122908532</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3362,19 +3356,19 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557989</v>
+        <v>557942</v>
       </c>
       <c r="R25" t="n">
-        <v>7045623</v>
+        <v>7045683</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3406,7 +3400,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3416,7 +3410,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,10 +3437,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122908532</v>
+        <v>122908440</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3455,30 +3449,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3487,10 +3482,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557942</v>
+        <v>557960</v>
       </c>
       <c r="R26" t="n">
-        <v>7045683</v>
+        <v>7045650</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,7 +3527,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,12 +3547,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122908497</v>
+        <v>122909723</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5180,47 +5180,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557969</v>
+        <v>558113</v>
       </c>
       <c r="R41" t="n">
-        <v>7045641</v>
+        <v>7045588</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5252,7 +5243,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5262,7 +5253,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5277,22 +5268,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122909723</v>
+        <v>122908497</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5301,38 +5292,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558113</v>
+        <v>557969</v>
       </c>
       <c r="R42" t="n">
-        <v>7045588</v>
+        <v>7045641</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5389,12 +5389,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122883501</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
+        <v>92236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122885158</v>
+        <v>122887408</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557925</v>
+        <v>558107</v>
       </c>
       <c r="R3" t="n">
-        <v>7045226</v>
+        <v>7045485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883141</v>
+        <v>122882954</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,31 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557872</v>
+        <v>557874</v>
       </c>
       <c r="R4" t="n">
-        <v>7045237</v>
+        <v>7045270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>+50 Ringhack på tall</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,7 +1023,7 @@
         <v>122887465</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1142,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122882954</v>
+        <v>122885158</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,7 +1167,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1191,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557874</v>
+        <v>557925</v>
       </c>
       <c r="R6" t="n">
-        <v>7045270</v>
+        <v>7045226</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,7 +1256,7 @@
         <v>122887288</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1375,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122887408</v>
+        <v>122883141</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1381,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558107</v>
+        <v>557872</v>
       </c>
       <c r="R8" t="n">
-        <v>7045485</v>
+        <v>7045237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1455,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>+50 Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122914573</v>
+        <v>122908497</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,38 +1499,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557892</v>
+        <v>557969</v>
       </c>
       <c r="R9" t="n">
-        <v>7045361</v>
+        <v>7045641</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1596,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122908738</v>
+        <v>122909331</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,34 +1624,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558014</v>
+        <v>557986</v>
       </c>
       <c r="R10" t="n">
-        <v>7045616</v>
+        <v>7045500</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122911743</v>
+        <v>122908440</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,34 +1741,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558114</v>
+        <v>557960</v>
       </c>
       <c r="R11" t="n">
-        <v>7045374</v>
+        <v>7045650</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1815,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122909860</v>
+        <v>122914413</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,38 +1859,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558133</v>
+        <v>557884</v>
       </c>
       <c r="R12" t="n">
-        <v>7045474</v>
+        <v>7045302</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1936,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,22 +1951,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122909459</v>
+        <v>122914606</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>90975</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,39 +1979,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557966</v>
+        <v>557893</v>
       </c>
       <c r="R13" t="n">
-        <v>7045501</v>
+        <v>7045351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,12 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,22 +2063,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122908422</v>
+        <v>122909860</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2073,39 +2091,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557977</v>
+        <v>558133</v>
       </c>
       <c r="R14" t="n">
-        <v>7045673</v>
+        <v>7045474</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,12 +2160,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,22 +2175,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122914405</v>
+        <v>122914868</v>
       </c>
       <c r="B15" t="n">
-        <v>92233</v>
+        <v>79851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,25 +2199,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557976</v>
+        <v>557948</v>
       </c>
       <c r="R15" t="n">
-        <v>7045210</v>
+        <v>7045384</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,22 +2287,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122908559</v>
+        <v>122908738</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,39 +2315,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557959</v>
+        <v>558014</v>
       </c>
       <c r="R16" t="n">
-        <v>7045628</v>
+        <v>7045616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,12 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2413,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122914413</v>
+        <v>122908779</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557884</v>
+        <v>557996</v>
       </c>
       <c r="R17" t="n">
-        <v>7045302</v>
+        <v>7045609</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2492,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2502,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,10 +2527,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122910281</v>
+        <v>122909987</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2545,21 +2543,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2569,10 +2567,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558178</v>
+        <v>558129</v>
       </c>
       <c r="R18" t="n">
-        <v>7045498</v>
+        <v>7045578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2604,7 +2602,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2614,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,10 +2639,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122914531</v>
+        <v>122914666</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2657,34 +2655,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557870</v>
+        <v>557892</v>
       </c>
       <c r="R19" t="n">
-        <v>7045346</v>
+        <v>7045356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2716,7 +2719,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2726,7 +2729,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122914606</v>
+        <v>122909523</v>
       </c>
       <c r="B20" t="n">
-        <v>90972</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2765,38 +2773,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557893</v>
+        <v>558123</v>
       </c>
       <c r="R20" t="n">
-        <v>7045351</v>
+        <v>7045531</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2828,7 +2840,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2850,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,10 +2877,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122912661</v>
+        <v>122908246</v>
       </c>
       <c r="B21" t="n">
-        <v>82553</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,34 +2893,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558113</v>
+        <v>557977</v>
       </c>
       <c r="R21" t="n">
-        <v>7045372</v>
+        <v>7045628</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2940,7 +2956,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2966,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2977,10 +2993,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122908146</v>
+        <v>122908532</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3012,7 +3028,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3021,10 +3037,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557988</v>
+        <v>557942</v>
       </c>
       <c r="R22" t="n">
-        <v>7045659</v>
+        <v>7045683</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3056,7 +3072,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3066,7 +3082,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3093,10 +3109,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122909987</v>
+        <v>122914308</v>
       </c>
       <c r="B23" t="n">
-        <v>90952</v>
+        <v>78769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3109,34 +3125,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558129</v>
+        <v>557955</v>
       </c>
       <c r="R23" t="n">
-        <v>7045578</v>
+        <v>7045351</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3168,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,10 +3221,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122908440</v>
+        <v>122914573</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,39 +3237,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557960</v>
+        <v>557892</v>
       </c>
       <c r="R24" t="n">
-        <v>7045650</v>
+        <v>7045361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3285,7 +3296,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3295,12 +3306,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,22 +3321,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122908181</v>
+        <v>122910006</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>79850</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,42 +3345,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557989</v>
+        <v>558154</v>
       </c>
       <c r="R25" t="n">
-        <v>7045623</v>
+        <v>7045445</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3406,7 +3408,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3416,7 +3418,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,22 +3433,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122908532</v>
+        <v>122908038</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3455,30 +3457,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3487,10 +3490,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557942</v>
+        <v>558017</v>
       </c>
       <c r="R26" t="n">
-        <v>7045683</v>
+        <v>7045654</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,7 +3525,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,7 +3535,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,10 +3567,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122914213</v>
+        <v>122909723</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,14 +3603,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557991</v>
+        <v>558113</v>
       </c>
       <c r="R27" t="n">
-        <v>7045335</v>
+        <v>7045588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3634,7 +3642,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3644,7 +3652,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3671,10 +3679,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122909331</v>
+        <v>122908146</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>98368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3683,43 +3691,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557986</v>
+        <v>557988</v>
       </c>
       <c r="R28" t="n">
-        <v>7045500</v>
+        <v>7045659</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,7 +3758,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3768,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3776,22 +3783,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122908038</v>
+        <v>122908181</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>98368</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3800,43 +3807,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558017</v>
+        <v>557989</v>
       </c>
       <c r="R29" t="n">
-        <v>7045654</v>
+        <v>7045623</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3868,7 +3874,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3878,12 +3884,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3910,10 +3911,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122914308</v>
+        <v>122909459</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3926,34 +3927,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557955</v>
+        <v>557966</v>
       </c>
       <c r="R30" t="n">
-        <v>7045351</v>
+        <v>7045501</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3985,7 +3991,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3995,7 +4001,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,22 +4021,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122908779</v>
+        <v>122909049</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4034,30 +4045,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4066,10 +4078,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557996</v>
+        <v>558048</v>
       </c>
       <c r="R31" t="n">
-        <v>7045609</v>
+        <v>7045527</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4101,7 +4113,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4111,7 +4123,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4126,22 +4143,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122909523</v>
+        <v>122913820</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4173,19 +4190,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558123</v>
+        <v>558157</v>
       </c>
       <c r="R32" t="n">
-        <v>7045531</v>
+        <v>7045329</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4217,7 +4234,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4227,7 +4244,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4254,10 +4271,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122913820</v>
+        <v>122914405</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>92236</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4266,42 +4283,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558157</v>
+        <v>557976</v>
       </c>
       <c r="R33" t="n">
-        <v>7045329</v>
+        <v>7045210</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4333,7 +4346,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4343,7 +4356,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4358,22 +4371,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122908377</v>
+        <v>122910281</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4406,14 +4419,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557960</v>
+        <v>558178</v>
       </c>
       <c r="R34" t="n">
-        <v>7045662</v>
+        <v>7045498</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4445,7 +4458,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4455,7 +4468,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4482,10 +4495,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910006</v>
+        <v>122911743</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4522,10 +4535,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558154</v>
+        <v>558114</v>
       </c>
       <c r="R35" t="n">
-        <v>7045445</v>
+        <v>7045374</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4557,7 +4570,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4567,7 +4580,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4594,10 +4607,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122908666</v>
+        <v>122912795</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>82556</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4610,34 +4623,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557951</v>
+        <v>558128</v>
       </c>
       <c r="R36" t="n">
-        <v>7045711</v>
+        <v>7045377</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4669,7 +4682,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4679,7 +4692,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4706,10 +4719,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122914334</v>
+        <v>122912661</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>82556</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4722,21 +4735,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4746,10 +4759,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557931</v>
+        <v>558113</v>
       </c>
       <c r="R37" t="n">
-        <v>7045323</v>
+        <v>7045372</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4781,7 +4794,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4791,7 +4804,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4821,7 +4834,7 @@
         <v>122908447</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4930,10 +4943,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122909049</v>
+        <v>122908666</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4946,39 +4959,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558048</v>
+        <v>557951</v>
       </c>
       <c r="R39" t="n">
-        <v>7045527</v>
+        <v>7045711</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5010,7 +5018,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5020,12 +5028,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5040,22 +5043,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122908246</v>
+        <v>122908422</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5085,21 +5088,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
         <v>557977</v>
       </c>
       <c r="R40" t="n">
-        <v>7045628</v>
+        <v>7045673</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5131,7 +5135,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5141,7 +5145,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5168,10 +5177,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122909723</v>
+        <v>122914334</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5204,14 +5213,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558113</v>
+        <v>557931</v>
       </c>
       <c r="R41" t="n">
-        <v>7045588</v>
+        <v>7045323</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5243,7 +5252,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5253,7 +5262,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5280,10 +5289,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122908497</v>
+        <v>122914531</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5292,47 +5301,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557969</v>
+        <v>557870</v>
       </c>
       <c r="R42" t="n">
-        <v>7045641</v>
+        <v>7045346</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5389,22 +5389,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122912795</v>
+        <v>122914213</v>
       </c>
       <c r="B43" t="n">
-        <v>82553</v>
+        <v>78769</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5417,21 +5417,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558128</v>
+        <v>557991</v>
       </c>
       <c r="R43" t="n">
-        <v>7045377</v>
+        <v>7045335</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5513,10 +5513,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122914868</v>
+        <v>122908559</v>
       </c>
       <c r="B44" t="n">
-        <v>79848</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5529,34 +5529,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557948</v>
+        <v>557959</v>
       </c>
       <c r="R44" t="n">
-        <v>7045384</v>
+        <v>7045628</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5588,7 +5593,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5598,7 +5603,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5613,22 +5623,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122914666</v>
+        <v>122908377</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5641,39 +5651,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557892</v>
+        <v>557960</v>
       </c>
       <c r="R45" t="n">
-        <v>7045356</v>
+        <v>7045662</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5705,7 +5710,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5715,12 +5720,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5750,7 +5750,7 @@
         <v>122909181</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5868,10 +5868,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123114009</v>
+        <v>123116920</v>
       </c>
       <c r="B47" t="n">
-        <v>90917</v>
+        <v>78153</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5880,25 +5880,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558050</v>
+        <v>557888</v>
       </c>
       <c r="R47" t="n">
-        <v>7045576</v>
+        <v>7045356</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5941,19 +5941,9 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5968,22 +5958,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123117683</v>
+        <v>123114354</v>
       </c>
       <c r="B48" t="n">
-        <v>78502</v>
+        <v>92236</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5992,25 +5982,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6020,10 +6010,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557966</v>
+        <v>557978</v>
       </c>
       <c r="R48" t="n">
-        <v>7045239</v>
+        <v>7045589</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6055,7 +6045,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6065,7 +6055,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,10 +6082,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123114354</v>
+        <v>123115166</v>
       </c>
       <c r="B49" t="n">
-        <v>92233</v>
+        <v>78414</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6104,25 +6094,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6132,10 +6122,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557978</v>
+        <v>557961</v>
       </c>
       <c r="R49" t="n">
-        <v>7045589</v>
+        <v>7045574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6167,7 +6157,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6177,7 +6167,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,10 +6194,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123116920</v>
+        <v>123114009</v>
       </c>
       <c r="B50" t="n">
-        <v>78150</v>
+        <v>90920</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6216,25 +6206,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6244,13 +6234,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557888</v>
+        <v>558050</v>
       </c>
       <c r="R50" t="n">
-        <v>7045356</v>
+        <v>7045576</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6277,9 +6267,19 @@
           <t>2025-03-12</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6294,22 +6294,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123117651</v>
+        <v>123115068</v>
       </c>
       <c r="B51" t="n">
-        <v>57589</v>
+        <v>92236</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6322,43 +6322,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557907</v>
+        <v>557961</v>
       </c>
       <c r="R51" t="n">
-        <v>7045262</v>
+        <v>7045587</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6390,7 +6381,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6400,7 +6391,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6427,10 +6418,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123119791</v>
+        <v>123117651</v>
       </c>
       <c r="B52" t="n">
-        <v>98365</v>
+        <v>57592</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6439,30 +6430,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6471,10 +6467,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557988</v>
+        <v>557907</v>
       </c>
       <c r="R52" t="n">
-        <v>7045172</v>
+        <v>7045262</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,7 +6502,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6516,7 +6512,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6543,10 +6539,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123115166</v>
+        <v>123117683</v>
       </c>
       <c r="B53" t="n">
-        <v>78411</v>
+        <v>78505</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6559,21 +6555,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6583,10 +6579,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557961</v>
+        <v>557966</v>
       </c>
       <c r="R53" t="n">
-        <v>7045574</v>
+        <v>7045239</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6618,7 +6614,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6628,7 +6624,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6655,10 +6651,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123115068</v>
+        <v>123115087</v>
       </c>
       <c r="B54" t="n">
-        <v>92233</v>
+        <v>56691</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6671,34 +6667,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557961</v>
+        <v>557957</v>
       </c>
       <c r="R54" t="n">
-        <v>7045587</v>
+        <v>7045576</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6730,7 +6731,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6740,7 +6741,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6767,10 +6768,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123115087</v>
+        <v>123119791</v>
       </c>
       <c r="B55" t="n">
-        <v>56688</v>
+        <v>98368</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6779,31 +6780,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557957</v>
+        <v>557988</v>
       </c>
       <c r="R55" t="n">
-        <v>7045576</v>
+        <v>7045172</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122883501</v>
+        <v>122883141</v>
       </c>
       <c r="B2" t="n">
-        <v>92236</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557908</v>
+        <v>557872</v>
       </c>
       <c r="R2" t="n">
-        <v>7045230</v>
+        <v>7045237</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>+50 Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122887408</v>
+        <v>122882954</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +809,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558107</v>
+        <v>557874</v>
       </c>
       <c r="R3" t="n">
-        <v>7045485</v>
+        <v>7045270</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122882954</v>
+        <v>122887408</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +930,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557874</v>
+        <v>558107</v>
       </c>
       <c r="R4" t="n">
-        <v>7045270</v>
+        <v>7045485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122887465</v>
+        <v>122883501</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>92238</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1042,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558046</v>
+        <v>557908</v>
       </c>
       <c r="R5" t="n">
-        <v>7045577</v>
+        <v>7045230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122885158</v>
+        <v>122887288</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,47 +1154,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557925</v>
+        <v>558116</v>
       </c>
       <c r="R6" t="n">
-        <v>7045226</v>
+        <v>7045369</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122887288</v>
+        <v>122887465</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1270,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558116</v>
+        <v>558046</v>
       </c>
       <c r="R7" t="n">
-        <v>7045369</v>
+        <v>7045577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122883141</v>
+        <v>122885158</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,31 +1378,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1410,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557872</v>
+        <v>557925</v>
       </c>
       <c r="R8" t="n">
-        <v>7045237</v>
+        <v>7045226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,12 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>+50 Ringhack på tall</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122908497</v>
+        <v>122908440</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,35 +1499,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1536,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557969</v>
+        <v>557960</v>
       </c>
       <c r="R9" t="n">
-        <v>7045641</v>
+        <v>7045650</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122909331</v>
+        <v>122909459</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,16 +1625,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1653,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557986</v>
+        <v>557966</v>
       </c>
       <c r="R10" t="n">
-        <v>7045500</v>
+        <v>7045501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1699,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122908440</v>
+        <v>122908146</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,31 +1743,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557960</v>
+        <v>557988</v>
       </c>
       <c r="R11" t="n">
-        <v>7045650</v>
+        <v>7045659</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,12 +1820,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,22 +1835,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122914413</v>
+        <v>122908779</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557884</v>
+        <v>557996</v>
       </c>
       <c r="R12" t="n">
-        <v>7045302</v>
+        <v>7045609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122914606</v>
+        <v>122910281</v>
       </c>
       <c r="B13" t="n">
-        <v>90975</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,34 +1979,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557893</v>
+        <v>558178</v>
       </c>
       <c r="R13" t="n">
-        <v>7045351</v>
+        <v>7045498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122909860</v>
+        <v>122912795</v>
       </c>
       <c r="B14" t="n">
-        <v>79850</v>
+        <v>82558</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2091,21 +2091,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558133</v>
+        <v>558128</v>
       </c>
       <c r="R14" t="n">
-        <v>7045474</v>
+        <v>7045377</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,22 +2175,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122914868</v>
+        <v>122908738</v>
       </c>
       <c r="B15" t="n">
-        <v>79851</v>
+        <v>79852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,21 +2203,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557948</v>
+        <v>558014</v>
       </c>
       <c r="R15" t="n">
-        <v>7045384</v>
+        <v>7045616</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,22 +2287,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122908738</v>
+        <v>122914666</v>
       </c>
       <c r="B16" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,34 +2315,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558014</v>
+        <v>557892</v>
       </c>
       <c r="R16" t="n">
-        <v>7045616</v>
+        <v>7045356</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2389,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,22 +2409,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908779</v>
+        <v>122908497</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2446,19 +2456,24 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557996</v>
+        <v>557969</v>
       </c>
       <c r="R17" t="n">
-        <v>7045609</v>
+        <v>7045641</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2515,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,22 +2530,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122909987</v>
+        <v>122908181</v>
       </c>
       <c r="B18" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,38 +2554,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558129</v>
+        <v>557989</v>
       </c>
       <c r="R18" t="n">
-        <v>7045578</v>
+        <v>7045623</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2602,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2612,7 +2631,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122914666</v>
+        <v>122909181</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,31 +2670,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2684,10 +2707,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557892</v>
+        <v>558033</v>
       </c>
       <c r="R19" t="n">
-        <v>7045356</v>
+        <v>7045487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2719,7 +2742,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,12 +2752,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,22 +2767,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122909523</v>
+        <v>122912661</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>82558</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2773,42 +2791,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558123</v>
+        <v>558113</v>
       </c>
       <c r="R20" t="n">
-        <v>7045531</v>
+        <v>7045372</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2840,7 +2854,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,7 +2864,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2877,10 +2891,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122908246</v>
+        <v>122914573</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2893,38 +2907,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557977</v>
+        <v>557892</v>
       </c>
       <c r="R21" t="n">
-        <v>7045628</v>
+        <v>7045361</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,7 +2966,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2966,7 +2976,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,10 +3003,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122908532</v>
+        <v>122908447</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3005,42 +3015,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557942</v>
+        <v>557958</v>
       </c>
       <c r="R22" t="n">
-        <v>7045683</v>
+        <v>7045677</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3072,7 +3078,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3082,7 +3088,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3109,10 +3115,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122914308</v>
+        <v>122909049</v>
       </c>
       <c r="B23" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3125,34 +3131,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>557955</v>
+        <v>558048</v>
       </c>
       <c r="R23" t="n">
-        <v>7045351</v>
+        <v>7045527</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,7 +3195,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3205,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,22 +3225,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122914573</v>
+        <v>122914413</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3233,38 +3249,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557892</v>
+        <v>557884</v>
       </c>
       <c r="R24" t="n">
-        <v>7045361</v>
+        <v>7045302</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3296,7 +3316,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,7 +3326,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,10 +3353,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122910006</v>
+        <v>122908377</v>
       </c>
       <c r="B25" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3349,34 +3369,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558154</v>
+        <v>557960</v>
       </c>
       <c r="R25" t="n">
-        <v>7045445</v>
+        <v>7045662</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3408,7 +3428,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3418,7 +3438,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3433,12 +3453,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3567,10 +3587,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122909723</v>
+        <v>122908559</v>
       </c>
       <c r="B27" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3583,34 +3603,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558113</v>
+        <v>557959</v>
       </c>
       <c r="R27" t="n">
-        <v>7045588</v>
+        <v>7045628</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3642,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3652,7 +3677,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3667,22 +3697,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122908146</v>
+        <v>122908666</v>
       </c>
       <c r="B28" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3691,42 +3721,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557988</v>
+        <v>557951</v>
       </c>
       <c r="R28" t="n">
-        <v>7045659</v>
+        <v>7045711</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3758,7 +3784,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3768,7 +3794,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,10 +3821,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122908181</v>
+        <v>122914334</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3807,42 +3833,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557989</v>
+        <v>557931</v>
       </c>
       <c r="R29" t="n">
-        <v>7045623</v>
+        <v>7045323</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3874,7 +3896,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3884,7 +3906,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3911,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122909459</v>
+        <v>122908246</v>
       </c>
       <c r="B30" t="n">
         <v>57481</v>
@@ -3944,10 +3966,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3956,10 +3977,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557966</v>
+        <v>557977</v>
       </c>
       <c r="R30" t="n">
-        <v>7045501</v>
+        <v>7045628</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3991,7 +4012,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4001,12 +4022,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4021,22 +4037,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122909049</v>
+        <v>122909987</v>
       </c>
       <c r="B31" t="n">
-        <v>57481</v>
+        <v>90957</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4049,39 +4065,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558048</v>
+        <v>558129</v>
       </c>
       <c r="R31" t="n">
-        <v>7045527</v>
+        <v>7045578</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4113,7 +4124,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4123,12 +4134,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,22 +4149,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122913820</v>
+        <v>122914868</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>79853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4167,42 +4173,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558157</v>
+        <v>557948</v>
       </c>
       <c r="R32" t="n">
-        <v>7045329</v>
+        <v>7045384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4234,7 +4236,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4244,7 +4246,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4271,10 +4273,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122914405</v>
+        <v>122909723</v>
       </c>
       <c r="B33" t="n">
-        <v>92236</v>
+        <v>78771</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4283,38 +4285,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557976</v>
+        <v>558113</v>
       </c>
       <c r="R33" t="n">
-        <v>7045210</v>
+        <v>7045588</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4346,7 +4348,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4356,7 +4358,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4371,22 +4373,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122910281</v>
+        <v>122911743</v>
       </c>
       <c r="B34" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4399,34 +4401,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558178</v>
+        <v>558114</v>
       </c>
       <c r="R34" t="n">
-        <v>7045498</v>
+        <v>7045374</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4458,7 +4460,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4468,7 +4470,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4483,22 +4485,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122911743</v>
+        <v>122914531</v>
       </c>
       <c r="B35" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4511,21 +4513,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4535,10 +4537,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558114</v>
+        <v>557870</v>
       </c>
       <c r="R35" t="n">
-        <v>7045374</v>
+        <v>7045346</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4570,7 +4572,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4580,7 +4582,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4595,22 +4597,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122912795</v>
+        <v>122914606</v>
       </c>
       <c r="B36" t="n">
-        <v>82556</v>
+        <v>90977</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4623,21 +4625,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4647,10 +4649,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558128</v>
+        <v>557893</v>
       </c>
       <c r="R36" t="n">
-        <v>7045377</v>
+        <v>7045351</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4682,7 +4684,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4692,7 +4694,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4719,10 +4721,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122912661</v>
+        <v>122909331</v>
       </c>
       <c r="B37" t="n">
-        <v>82556</v>
+        <v>57497</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4735,34 +4737,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558113</v>
+        <v>557986</v>
       </c>
       <c r="R37" t="n">
-        <v>7045372</v>
+        <v>7045500</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4794,7 +4801,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4804,7 +4811,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4819,22 +4826,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122908447</v>
+        <v>122914213</v>
       </c>
       <c r="B38" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4867,14 +4874,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557958</v>
+        <v>557991</v>
       </c>
       <c r="R38" t="n">
-        <v>7045677</v>
+        <v>7045335</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4906,7 +4913,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4916,7 +4923,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4943,10 +4950,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122908666</v>
+        <v>122908532</v>
       </c>
       <c r="B39" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4955,38 +4962,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557951</v>
+        <v>557942</v>
       </c>
       <c r="R39" t="n">
-        <v>7045711</v>
+        <v>7045683</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5018,7 +5029,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5028,7 +5039,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5055,10 +5066,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122908422</v>
+        <v>122909523</v>
       </c>
       <c r="B40" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5067,43 +5078,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557977</v>
+        <v>558123</v>
       </c>
       <c r="R40" t="n">
-        <v>7045673</v>
+        <v>7045531</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5135,7 +5145,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5145,12 +5155,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5177,10 +5182,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122914334</v>
+        <v>122910006</v>
       </c>
       <c r="B41" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5193,21 +5198,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557931</v>
+        <v>558154</v>
       </c>
       <c r="R41" t="n">
-        <v>7045323</v>
+        <v>7045445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5252,7 +5257,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5262,7 +5267,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5277,22 +5282,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122914531</v>
+        <v>122913820</v>
       </c>
       <c r="B42" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5301,38 +5306,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>557870</v>
+        <v>558157</v>
       </c>
       <c r="R42" t="n">
-        <v>7045346</v>
+        <v>7045329</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5364,7 +5373,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5374,7 +5383,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5401,10 +5410,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122914213</v>
+        <v>122909860</v>
       </c>
       <c r="B43" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5417,21 +5426,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5441,10 +5450,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557991</v>
+        <v>558133</v>
       </c>
       <c r="R43" t="n">
-        <v>7045335</v>
+        <v>7045474</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5476,7 +5485,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5486,7 +5495,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5501,22 +5510,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122908559</v>
+        <v>122914405</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>92238</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5525,43 +5534,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557959</v>
+        <v>557976</v>
       </c>
       <c r="R44" t="n">
-        <v>7045628</v>
+        <v>7045210</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5593,7 +5597,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5603,12 +5607,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5635,10 +5634,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122908377</v>
+        <v>122914308</v>
       </c>
       <c r="B45" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5671,14 +5670,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557960</v>
+        <v>557955</v>
       </c>
       <c r="R45" t="n">
-        <v>7045662</v>
+        <v>7045351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5710,7 +5709,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5720,7 +5719,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5747,10 +5746,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122909181</v>
+        <v>122908422</v>
       </c>
       <c r="B46" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5759,47 +5758,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558033</v>
+        <v>557977</v>
       </c>
       <c r="R46" t="n">
-        <v>7045487</v>
+        <v>7045673</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5831,7 +5826,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5841,7 +5836,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5856,22 +5856,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123116920</v>
+        <v>123114354</v>
       </c>
       <c r="B47" t="n">
-        <v>78153</v>
+        <v>92238</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5880,25 +5880,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557888</v>
+        <v>557978</v>
       </c>
       <c r="R47" t="n">
-        <v>7045356</v>
+        <v>7045589</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5941,9 +5941,19 @@
           <t>2025-03-12</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5958,22 +5968,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123114354</v>
+        <v>123117651</v>
       </c>
       <c r="B48" t="n">
-        <v>92236</v>
+        <v>57592</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5986,34 +5996,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557978</v>
+        <v>557907</v>
       </c>
       <c r="R48" t="n">
-        <v>7045589</v>
+        <v>7045262</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6045,7 +6064,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6055,7 +6074,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6082,10 +6101,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123115166</v>
+        <v>123114009</v>
       </c>
       <c r="B49" t="n">
-        <v>78414</v>
+        <v>90922</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6094,25 +6113,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6122,10 +6141,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557961</v>
+        <v>558050</v>
       </c>
       <c r="R49" t="n">
-        <v>7045574</v>
+        <v>7045576</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6157,7 +6176,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6167,7 +6186,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6194,10 +6213,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123114009</v>
+        <v>123119791</v>
       </c>
       <c r="B50" t="n">
-        <v>90920</v>
+        <v>98370</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6206,38 +6225,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558050</v>
+        <v>557988</v>
       </c>
       <c r="R50" t="n">
-        <v>7045576</v>
+        <v>7045172</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6269,7 +6292,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6279,7 +6302,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6309,7 +6332,7 @@
         <v>123115068</v>
       </c>
       <c r="B51" t="n">
-        <v>92236</v>
+        <v>92238</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6418,10 +6441,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123117651</v>
+        <v>123116920</v>
       </c>
       <c r="B52" t="n">
-        <v>57592</v>
+        <v>78155</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6430,50 +6453,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103031</v>
+        <v>6437</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557907</v>
+        <v>557888</v>
       </c>
       <c r="R52" t="n">
-        <v>7045262</v>
+        <v>7045356</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6500,19 +6514,9 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6527,12 +6531,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6542,7 +6546,7 @@
         <v>123117683</v>
       </c>
       <c r="B53" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6651,10 +6655,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123115087</v>
+        <v>123115166</v>
       </c>
       <c r="B54" t="n">
-        <v>56691</v>
+        <v>78416</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6663,43 +6667,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557957</v>
+        <v>557961</v>
       </c>
       <c r="R54" t="n">
-        <v>7045576</v>
+        <v>7045574</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6731,7 +6730,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6741,7 +6740,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6768,10 +6767,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123119791</v>
+        <v>123115087</v>
       </c>
       <c r="B55" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6780,30 +6779,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557988</v>
+        <v>557957</v>
       </c>
       <c r="R55" t="n">
-        <v>7045172</v>
+        <v>7045576</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -2187,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122908738</v>
+        <v>122908497</v>
       </c>
       <c r="B15" t="n">
-        <v>79852</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,38 +2199,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558014</v>
+        <v>557969</v>
       </c>
       <c r="R15" t="n">
-        <v>7045616</v>
+        <v>7045641</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2262,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2281,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2421,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908497</v>
+        <v>122908738</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>79852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2433,47 +2442,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557969</v>
+        <v>558014</v>
       </c>
       <c r="R17" t="n">
-        <v>7045641</v>
+        <v>7045616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122883141</v>
+        <v>122887465</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>557872</v>
+        <v>558046</v>
       </c>
       <c r="R2" t="n">
-        <v>7045237</v>
+        <v>7045577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>+50 Ringhack på tall</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122882954</v>
+        <v>122887408</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>79853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557874</v>
+        <v>558107</v>
       </c>
       <c r="R3" t="n">
-        <v>7045270</v>
+        <v>7045485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122887408</v>
+        <v>122885158</v>
       </c>
       <c r="B4" t="n">
-        <v>79852</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,38 +911,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558107</v>
+        <v>557925</v>
       </c>
       <c r="R4" t="n">
-        <v>7045485</v>
+        <v>7045226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122883501</v>
+        <v>122887288</v>
       </c>
       <c r="B5" t="n">
-        <v>92238</v>
+        <v>79853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557908</v>
+        <v>558116</v>
       </c>
       <c r="R5" t="n">
-        <v>7045230</v>
+        <v>7045369</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122887288</v>
+        <v>122883501</v>
       </c>
       <c r="B6" t="n">
-        <v>79852</v>
+        <v>92244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,25 +1144,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558116</v>
+        <v>557908</v>
       </c>
       <c r="R6" t="n">
-        <v>7045369</v>
+        <v>7045230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122887465</v>
+        <v>122882954</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,38 +1256,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558046</v>
+        <v>557874</v>
       </c>
       <c r="R7" t="n">
-        <v>7045577</v>
+        <v>7045270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122885158</v>
+        <v>122883141</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,35 +1377,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1415,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557925</v>
+        <v>557872</v>
       </c>
       <c r="R8" t="n">
-        <v>7045226</v>
+        <v>7045237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1455,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>+50 Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122908440</v>
+        <v>122914308</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,39 +1503,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557960</v>
+        <v>557955</v>
       </c>
       <c r="R9" t="n">
-        <v>7045650</v>
+        <v>7045351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122909459</v>
+        <v>122914573</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,39 +1615,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557966</v>
+        <v>557892</v>
       </c>
       <c r="R10" t="n">
-        <v>7045501</v>
+        <v>7045361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,12 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,22 +1699,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122908146</v>
+        <v>122909331</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,42 +1723,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557988</v>
+        <v>557986</v>
       </c>
       <c r="R11" t="n">
-        <v>7045659</v>
+        <v>7045500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,22 +1816,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122908779</v>
+        <v>122911743</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>79853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,42 +1840,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557996</v>
+        <v>558114</v>
       </c>
       <c r="R12" t="n">
-        <v>7045609</v>
+        <v>7045374</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,22 +1928,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122910281</v>
+        <v>122908497</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,38 +1952,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558178</v>
+        <v>557969</v>
       </c>
       <c r="R13" t="n">
-        <v>7045498</v>
+        <v>7045641</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,22 +2049,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122912795</v>
+        <v>122908181</v>
       </c>
       <c r="B14" t="n">
-        <v>82558</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,38 +2073,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558128</v>
+        <v>557989</v>
       </c>
       <c r="R14" t="n">
-        <v>7045377</v>
+        <v>7045623</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,7 +2150,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122908497</v>
+        <v>122909181</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,14 +2222,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557969</v>
+        <v>558033</v>
       </c>
       <c r="R15" t="n">
-        <v>7045641</v>
+        <v>7045487</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2271,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2271,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,10 +2298,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122914666</v>
+        <v>122908532</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2320,43 +2310,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557892</v>
+        <v>557942</v>
       </c>
       <c r="R16" t="n">
-        <v>7045356</v>
+        <v>7045683</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2388,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,12 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908738</v>
+        <v>122910006</v>
       </c>
       <c r="B17" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2470,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558014</v>
+        <v>558154</v>
       </c>
       <c r="R17" t="n">
-        <v>7045616</v>
+        <v>7045445</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122908181</v>
+        <v>122909049</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2554,30 +2538,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2586,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557989</v>
+        <v>558048</v>
       </c>
       <c r="R18" t="n">
-        <v>7045623</v>
+        <v>7045527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2621,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2631,7 +2616,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,22 +2636,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122909181</v>
+        <v>122909523</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2693,24 +2683,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558033</v>
+        <v>558123</v>
       </c>
       <c r="R19" t="n">
-        <v>7045487</v>
+        <v>7045531</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,7 +2727,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2752,7 +2737,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2767,22 +2752,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122912661</v>
+        <v>122908779</v>
       </c>
       <c r="B20" t="n">
-        <v>82558</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,38 +2776,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558113</v>
+        <v>557996</v>
       </c>
       <c r="R20" t="n">
-        <v>7045372</v>
+        <v>7045609</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2854,7 +2843,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2864,7 +2853,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,10 +2880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122914573</v>
+        <v>122910281</v>
       </c>
       <c r="B21" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2927,14 +2916,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>557892</v>
+        <v>558178</v>
       </c>
       <c r="R21" t="n">
-        <v>7045361</v>
+        <v>7045498</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2976,7 +2965,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3003,10 +2992,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122908447</v>
+        <v>122914213</v>
       </c>
       <c r="B22" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,14 +3028,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557958</v>
+        <v>557991</v>
       </c>
       <c r="R22" t="n">
-        <v>7045677</v>
+        <v>7045335</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3078,7 +3067,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3088,7 +3077,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,10 +3104,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122909049</v>
+        <v>122914868</v>
       </c>
       <c r="B23" t="n">
-        <v>57481</v>
+        <v>79854</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3131,39 +3120,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558048</v>
+        <v>557948</v>
       </c>
       <c r="R23" t="n">
-        <v>7045527</v>
+        <v>7045384</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3195,7 +3179,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3205,12 +3189,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3225,22 +3204,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122914413</v>
+        <v>122912795</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>82559</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,42 +3228,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557884</v>
+        <v>558128</v>
       </c>
       <c r="R24" t="n">
-        <v>7045302</v>
+        <v>7045377</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3316,7 +3291,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3326,7 +3301,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3353,10 +3328,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122908377</v>
+        <v>122909860</v>
       </c>
       <c r="B25" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3369,34 +3344,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557960</v>
+        <v>558133</v>
       </c>
       <c r="R25" t="n">
-        <v>7045662</v>
+        <v>7045474</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3428,7 +3403,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3438,7 +3413,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3453,22 +3428,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122908038</v>
+        <v>122912661</v>
       </c>
       <c r="B26" t="n">
-        <v>57481</v>
+        <v>82559</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,39 +3456,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558017</v>
+        <v>558113</v>
       </c>
       <c r="R26" t="n">
-        <v>7045654</v>
+        <v>7045372</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3545,7 +3515,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3555,12 +3525,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3587,10 +3552,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122908559</v>
+        <v>122909723</v>
       </c>
       <c r="B27" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3603,39 +3568,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557959</v>
+        <v>558113</v>
       </c>
       <c r="R27" t="n">
-        <v>7045628</v>
+        <v>7045588</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3667,7 +3627,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,12 +3637,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3697,12 +3652,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3712,7 +3667,7 @@
         <v>122908666</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3821,10 +3776,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122914334</v>
+        <v>122914405</v>
       </c>
       <c r="B29" t="n">
-        <v>78771</v>
+        <v>92244</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3833,25 +3788,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3861,10 +3816,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557931</v>
+        <v>557976</v>
       </c>
       <c r="R29" t="n">
-        <v>7045323</v>
+        <v>7045210</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3896,7 +3851,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3906,7 +3861,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,12 +3876,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4049,10 +4004,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122909987</v>
+        <v>122909459</v>
       </c>
       <c r="B31" t="n">
-        <v>90957</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4065,34 +4020,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558129</v>
+        <v>557966</v>
       </c>
       <c r="R31" t="n">
-        <v>7045578</v>
+        <v>7045501</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4124,7 +4084,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4134,7 +4094,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4149,19 +4114,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122914868</v>
+        <v>122908738</v>
       </c>
       <c r="B32" t="n">
         <v>79853</v>
@@ -4177,21 +4142,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4201,10 +4166,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557948</v>
+        <v>558014</v>
       </c>
       <c r="R32" t="n">
-        <v>7045384</v>
+        <v>7045616</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4236,7 +4201,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4246,7 +4211,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4261,22 +4226,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122909723</v>
+        <v>122914334</v>
       </c>
       <c r="B33" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4309,14 +4274,14 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558113</v>
+        <v>557931</v>
       </c>
       <c r="R33" t="n">
-        <v>7045588</v>
+        <v>7045323</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4348,7 +4313,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4358,7 +4323,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4385,10 +4350,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122911743</v>
+        <v>122908559</v>
       </c>
       <c r="B34" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4401,34 +4366,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558114</v>
+        <v>557959</v>
       </c>
       <c r="R34" t="n">
-        <v>7045374</v>
+        <v>7045628</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4460,7 +4430,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4470,7 +4440,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4497,10 +4472,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122914531</v>
+        <v>122914413</v>
       </c>
       <c r="B35" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4509,38 +4484,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>557870</v>
+        <v>557884</v>
       </c>
       <c r="R35" t="n">
-        <v>7045346</v>
+        <v>7045302</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4572,7 +4551,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4582,7 +4561,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4609,10 +4588,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122914606</v>
+        <v>122909987</v>
       </c>
       <c r="B36" t="n">
-        <v>90977</v>
+        <v>90963</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4625,34 +4604,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557893</v>
+        <v>558129</v>
       </c>
       <c r="R36" t="n">
-        <v>7045351</v>
+        <v>7045578</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4684,7 +4663,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4694,7 +4673,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4721,10 +4700,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122909331</v>
+        <v>122914606</v>
       </c>
       <c r="B37" t="n">
-        <v>57497</v>
+        <v>90983</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4737,39 +4716,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557986</v>
+        <v>557893</v>
       </c>
       <c r="R37" t="n">
-        <v>7045500</v>
+        <v>7045351</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4801,7 +4775,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4811,7 +4785,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4826,22 +4800,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122914213</v>
+        <v>122908440</v>
       </c>
       <c r="B38" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4854,34 +4828,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557991</v>
+        <v>557960</v>
       </c>
       <c r="R38" t="n">
-        <v>7045335</v>
+        <v>7045650</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4913,7 +4892,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4923,7 +4902,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4938,22 +4922,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122908532</v>
+        <v>122908447</v>
       </c>
       <c r="B39" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4962,42 +4946,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557942</v>
+        <v>557958</v>
       </c>
       <c r="R39" t="n">
-        <v>7045683</v>
+        <v>7045677</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5029,7 +5009,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5039,7 +5019,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5066,10 +5046,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122909523</v>
+        <v>122908422</v>
       </c>
       <c r="B40" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5078,42 +5058,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558123</v>
+        <v>557977</v>
       </c>
       <c r="R40" t="n">
-        <v>7045531</v>
+        <v>7045673</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5145,7 +5126,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5155,7 +5136,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5182,10 +5168,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122910006</v>
+        <v>122908038</v>
       </c>
       <c r="B41" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5198,34 +5184,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558154</v>
+        <v>558017</v>
       </c>
       <c r="R41" t="n">
-        <v>7045445</v>
+        <v>7045654</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5257,7 +5248,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5267,7 +5258,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5282,22 +5278,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122913820</v>
+        <v>122914666</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5306,30 +5302,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5338,10 +5335,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558157</v>
+        <v>557892</v>
       </c>
       <c r="R42" t="n">
-        <v>7045329</v>
+        <v>7045356</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5373,7 +5370,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5383,7 +5380,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5410,10 +5412,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122909860</v>
+        <v>122913820</v>
       </c>
       <c r="B43" t="n">
-        <v>79852</v>
+        <v>98376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5422,38 +5424,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558133</v>
+        <v>558157</v>
       </c>
       <c r="R43" t="n">
-        <v>7045474</v>
+        <v>7045329</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5485,7 +5491,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5495,7 +5501,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5510,22 +5516,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122914405</v>
+        <v>122908146</v>
       </c>
       <c r="B44" t="n">
-        <v>92238</v>
+        <v>98376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5534,38 +5540,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557976</v>
+        <v>557988</v>
       </c>
       <c r="R44" t="n">
-        <v>7045210</v>
+        <v>7045659</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5597,7 +5607,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5607,7 +5617,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5622,22 +5632,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122914308</v>
+        <v>122908377</v>
       </c>
       <c r="B45" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5670,14 +5680,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557955</v>
+        <v>557960</v>
       </c>
       <c r="R45" t="n">
-        <v>7045351</v>
+        <v>7045662</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5709,7 +5719,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5719,7 +5729,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5746,10 +5756,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122908422</v>
+        <v>122914531</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5762,39 +5772,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>557977</v>
+        <v>557870</v>
       </c>
       <c r="R46" t="n">
-        <v>7045673</v>
+        <v>7045346</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5826,7 +5831,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5836,12 +5841,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5871,7 +5871,7 @@
         <v>123114354</v>
       </c>
       <c r="B47" t="n">
-        <v>92238</v>
+        <v>92244</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5980,10 +5980,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123117651</v>
+        <v>123114009</v>
       </c>
       <c r="B48" t="n">
-        <v>57592</v>
+        <v>90928</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5996,43 +5996,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557907</v>
+        <v>558050</v>
       </c>
       <c r="R48" t="n">
-        <v>7045262</v>
+        <v>7045576</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6064,7 +6055,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6074,7 +6065,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6101,10 +6092,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123114009</v>
+        <v>123115166</v>
       </c>
       <c r="B49" t="n">
-        <v>90922</v>
+        <v>78417</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6113,25 +6104,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6141,10 +6132,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558050</v>
+        <v>557961</v>
       </c>
       <c r="R49" t="n">
-        <v>7045576</v>
+        <v>7045574</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6176,7 +6167,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6186,7 +6177,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6213,10 +6204,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123119791</v>
+        <v>123115087</v>
       </c>
       <c r="B50" t="n">
-        <v>98370</v>
+        <v>56691</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6225,30 +6216,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6257,10 +6249,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557988</v>
+        <v>557957</v>
       </c>
       <c r="R50" t="n">
-        <v>7045172</v>
+        <v>7045576</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6292,7 +6284,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6302,7 +6294,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6332,7 +6324,7 @@
         <v>123115068</v>
       </c>
       <c r="B51" t="n">
-        <v>92238</v>
+        <v>92244</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6441,10 +6433,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123116920</v>
+        <v>123117651</v>
       </c>
       <c r="B52" t="n">
-        <v>78155</v>
+        <v>57592</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6453,41 +6445,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>103031</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557888</v>
+        <v>557907</v>
       </c>
       <c r="R52" t="n">
-        <v>7045356</v>
+        <v>7045262</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6514,9 +6515,19 @@
           <t>2025-03-12</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6531,22 +6542,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123117683</v>
+        <v>123116920</v>
       </c>
       <c r="B53" t="n">
-        <v>78507</v>
+        <v>78156</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6559,21 +6570,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6583,13 +6594,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557966</v>
+        <v>557888</v>
       </c>
       <c r="R53" t="n">
-        <v>7045239</v>
+        <v>7045356</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6616,19 +6627,9 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6643,22 +6644,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123115166</v>
+        <v>123117683</v>
       </c>
       <c r="B54" t="n">
-        <v>78416</v>
+        <v>78508</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6671,21 +6672,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6695,10 +6696,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557961</v>
+        <v>557966</v>
       </c>
       <c r="R54" t="n">
-        <v>7045574</v>
+        <v>7045239</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6730,7 +6731,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6740,7 +6741,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6767,10 +6768,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123115087</v>
+        <v>123119791</v>
       </c>
       <c r="B55" t="n">
-        <v>56691</v>
+        <v>98376</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6779,31 +6780,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557957</v>
+        <v>557988</v>
       </c>
       <c r="R55" t="n">
-        <v>7045576</v>
+        <v>7045172</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -1487,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122908738</v>
+        <v>122909459</v>
       </c>
       <c r="B9" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,34 +1503,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558014</v>
+        <v>557966</v>
       </c>
       <c r="R9" t="n">
-        <v>7045616</v>
+        <v>7045501</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122908181</v>
+        <v>122908038</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,42 +1621,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557989</v>
+        <v>558017</v>
       </c>
       <c r="R10" t="n">
-        <v>7045623</v>
+        <v>7045654</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1699,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,10 +1731,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122908532</v>
+        <v>122914308</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,42 +1743,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557942</v>
+        <v>557955</v>
       </c>
       <c r="R11" t="n">
-        <v>7045683</v>
+        <v>7045351</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1806,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1816,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122910006</v>
+        <v>122908738</v>
       </c>
       <c r="B12" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558154</v>
+        <v>558014</v>
       </c>
       <c r="R12" t="n">
-        <v>7045445</v>
+        <v>7045616</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122908422</v>
+        <v>122908532</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,31 +1967,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1988,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557977</v>
+        <v>557942</v>
       </c>
       <c r="R13" t="n">
-        <v>7045673</v>
+        <v>7045683</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,12 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,10 +2071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122912661</v>
+        <v>122909723</v>
       </c>
       <c r="B14" t="n">
-        <v>82562</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,34 +2087,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>558113</v>
       </c>
       <c r="R14" t="n">
-        <v>7045372</v>
+        <v>7045588</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2156,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122914666</v>
+        <v>122908246</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2210,10 +2216,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2222,10 +2227,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557892</v>
+        <v>557977</v>
       </c>
       <c r="R15" t="n">
-        <v>7045356</v>
+        <v>7045628</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,12 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122908246</v>
+        <v>122914413</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,30 +2311,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557977</v>
+        <v>557884</v>
       </c>
       <c r="R16" t="n">
-        <v>7045628</v>
+        <v>7045302</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908146</v>
+        <v>122908440</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,30 +2427,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2459,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557988</v>
+        <v>557960</v>
       </c>
       <c r="R17" t="n">
-        <v>7045659</v>
+        <v>7045650</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2494,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,7 +2505,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,22 +2525,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122914405</v>
+        <v>122909331</v>
       </c>
       <c r="B18" t="n">
-        <v>92247</v>
+        <v>57503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2543,38 +2549,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557976</v>
+        <v>557986</v>
       </c>
       <c r="R18" t="n">
-        <v>7045210</v>
+        <v>7045500</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2617,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2627,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2654,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122909723</v>
+        <v>122908559</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,34 +2670,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558113</v>
+        <v>557959</v>
       </c>
       <c r="R19" t="n">
-        <v>7045588</v>
+        <v>7045628</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2718,7 +2734,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2744,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,22 +2764,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122908440</v>
+        <v>122909049</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,19 +2812,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>557960</v>
+        <v>558048</v>
       </c>
       <c r="R20" t="n">
-        <v>7045650</v>
+        <v>7045527</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2835,7 +2856,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2845,7 +2866,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2877,10 +2898,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122913820</v>
+        <v>122912795</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>82568</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,42 +2910,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558157</v>
+        <v>558128</v>
       </c>
       <c r="R21" t="n">
-        <v>7045329</v>
+        <v>7045377</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2956,7 +2973,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2966,7 +2983,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2993,10 +3010,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122908497</v>
+        <v>122914606</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>91003</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3005,47 +3022,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557969</v>
+        <v>557893</v>
       </c>
       <c r="R22" t="n">
-        <v>7045641</v>
+        <v>7045351</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3077,7 +3085,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3087,7 +3095,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3102,22 +3110,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122910281</v>
+        <v>122914666</v>
       </c>
       <c r="B23" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3130,34 +3138,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558178</v>
+        <v>557892</v>
       </c>
       <c r="R23" t="n">
-        <v>7045498</v>
+        <v>7045356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3189,7 +3202,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3199,7 +3212,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3226,10 +3244,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122914213</v>
+        <v>122908779</v>
       </c>
       <c r="B24" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3238,38 +3256,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557991</v>
+        <v>557996</v>
       </c>
       <c r="R24" t="n">
-        <v>7045335</v>
+        <v>7045609</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3301,7 +3323,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3311,7 +3333,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3338,10 +3360,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122908666</v>
+        <v>122914405</v>
       </c>
       <c r="B25" t="n">
-        <v>78775</v>
+        <v>92264</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3350,38 +3372,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557951</v>
+        <v>557976</v>
       </c>
       <c r="R25" t="n">
-        <v>7045711</v>
+        <v>7045210</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3413,7 +3435,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3423,7 +3445,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,22 +3460,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122909181</v>
+        <v>122908666</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3462,47 +3484,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558033</v>
+        <v>557951</v>
       </c>
       <c r="R26" t="n">
-        <v>7045487</v>
+        <v>7045711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3534,7 +3547,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3544,7 +3557,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,22 +3572,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122912795</v>
+        <v>122914531</v>
       </c>
       <c r="B27" t="n">
-        <v>82562</v>
+        <v>78781</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3587,21 +3600,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3611,10 +3624,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558128</v>
+        <v>557870</v>
       </c>
       <c r="R27" t="n">
-        <v>7045377</v>
+        <v>7045346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3646,7 +3659,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3656,7 +3669,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3683,10 +3696,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122909331</v>
+        <v>122914213</v>
       </c>
       <c r="B28" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3699,39 +3712,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557986</v>
+        <v>557991</v>
       </c>
       <c r="R28" t="n">
-        <v>7045500</v>
+        <v>7045335</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3763,7 +3771,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3773,7 +3781,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,22 +3796,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122909459</v>
+        <v>122909860</v>
       </c>
       <c r="B29" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3816,39 +3824,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>557966</v>
+        <v>558133</v>
       </c>
       <c r="R29" t="n">
-        <v>7045501</v>
+        <v>7045474</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3880,7 +3883,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3890,12 +3893,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3922,10 +3920,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122908559</v>
+        <v>122913820</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3934,31 +3932,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3967,10 +3964,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>557959</v>
+        <v>558157</v>
       </c>
       <c r="R30" t="n">
-        <v>7045628</v>
+        <v>7045329</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4002,7 +3999,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4012,12 +4009,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4032,22 +4024,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122909523</v>
+        <v>122908497</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4079,19 +4071,24 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558123</v>
+        <v>557969</v>
       </c>
       <c r="R31" t="n">
-        <v>7045531</v>
+        <v>7045641</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4123,7 +4120,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4133,7 +4130,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,22 +4145,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122914531</v>
+        <v>122910281</v>
       </c>
       <c r="B32" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4196,14 +4193,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>557870</v>
+        <v>558178</v>
       </c>
       <c r="R32" t="n">
-        <v>7045346</v>
+        <v>7045498</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4235,7 +4232,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4245,7 +4242,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4275,7 +4272,7 @@
         <v>122914334</v>
       </c>
       <c r="B33" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4384,10 +4381,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122914868</v>
+        <v>122908377</v>
       </c>
       <c r="B34" t="n">
-        <v>79857</v>
+        <v>78781</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4400,34 +4397,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557948</v>
+        <v>557960</v>
       </c>
       <c r="R34" t="n">
-        <v>7045384</v>
+        <v>7045662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4459,7 +4456,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4469,7 +4466,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4496,10 +4493,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122908038</v>
+        <v>122910006</v>
       </c>
       <c r="B35" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4512,39 +4509,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558017</v>
+        <v>558154</v>
       </c>
       <c r="R35" t="n">
-        <v>7045654</v>
+        <v>7045445</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4576,7 +4568,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4586,12 +4578,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4606,22 +4593,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122914308</v>
+        <v>122914573</v>
       </c>
       <c r="B36" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4658,10 +4645,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557955</v>
+        <v>557892</v>
       </c>
       <c r="R36" t="n">
-        <v>7045351</v>
+        <v>7045361</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4693,7 +4680,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4703,7 +4690,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4730,10 +4717,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122909049</v>
+        <v>122914868</v>
       </c>
       <c r="B37" t="n">
-        <v>57481</v>
+        <v>79863</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4746,39 +4733,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558048</v>
+        <v>557948</v>
       </c>
       <c r="R37" t="n">
-        <v>7045527</v>
+        <v>7045384</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4810,7 +4792,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4820,12 +4802,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4840,22 +4817,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122908447</v>
+        <v>122908422</v>
       </c>
       <c r="B38" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4868,34 +4845,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>557958</v>
+        <v>557977</v>
       </c>
       <c r="R38" t="n">
-        <v>7045677</v>
+        <v>7045673</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4927,7 +4909,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4937,7 +4919,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4964,10 +4951,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122908779</v>
+        <v>122911743</v>
       </c>
       <c r="B39" t="n">
-        <v>98379</v>
+        <v>79862</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4976,42 +4963,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>557996</v>
+        <v>558114</v>
       </c>
       <c r="R39" t="n">
-        <v>7045609</v>
+        <v>7045374</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5043,7 +5026,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5053,7 +5036,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5068,22 +5051,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122914413</v>
+        <v>122909181</v>
       </c>
       <c r="B40" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5115,7 +5098,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5124,10 +5112,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>557884</v>
+        <v>558033</v>
       </c>
       <c r="R40" t="n">
-        <v>7045302</v>
+        <v>7045487</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5159,7 +5147,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5169,7 +5157,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5184,22 +5172,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122911743</v>
+        <v>122908447</v>
       </c>
       <c r="B41" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5212,34 +5200,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558114</v>
+        <v>557958</v>
       </c>
       <c r="R41" t="n">
-        <v>7045374</v>
+        <v>7045677</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5271,7 +5259,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5281,7 +5269,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5296,22 +5284,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122909860</v>
+        <v>122909987</v>
       </c>
       <c r="B42" t="n">
-        <v>79856</v>
+        <v>90983</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5324,34 +5312,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558133</v>
+        <v>558129</v>
       </c>
       <c r="R42" t="n">
-        <v>7045474</v>
+        <v>7045578</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5383,7 +5371,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5393,7 +5381,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5408,22 +5396,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122908377</v>
+        <v>122908181</v>
       </c>
       <c r="B43" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5432,38 +5420,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557960</v>
+        <v>557989</v>
       </c>
       <c r="R43" t="n">
-        <v>7045662</v>
+        <v>7045623</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5495,7 +5487,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5505,7 +5497,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5532,10 +5524,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122914573</v>
+        <v>122908146</v>
       </c>
       <c r="B44" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5544,38 +5536,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557892</v>
+        <v>557988</v>
       </c>
       <c r="R44" t="n">
-        <v>7045361</v>
+        <v>7045659</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5607,7 +5603,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5617,7 +5613,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5644,10 +5640,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122914606</v>
+        <v>122909523</v>
       </c>
       <c r="B45" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5656,38 +5652,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>557893</v>
+        <v>558123</v>
       </c>
       <c r="R45" t="n">
-        <v>7045351</v>
+        <v>7045531</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5756,10 +5756,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122909987</v>
+        <v>122912661</v>
       </c>
       <c r="B46" t="n">
-        <v>90966</v>
+        <v>82568</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5772,34 +5772,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558129</v>
+        <v>558113</v>
       </c>
       <c r="R46" t="n">
-        <v>7045578</v>
+        <v>7045372</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5871,7 +5871,7 @@
         <v>123114009</v>
       </c>
       <c r="B47" t="n">
-        <v>90931</v>
+        <v>90948</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5980,10 +5980,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123117651</v>
+        <v>123116920</v>
       </c>
       <c r="B48" t="n">
-        <v>57592</v>
+        <v>78165</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5992,50 +5992,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557907</v>
+        <v>557888</v>
       </c>
       <c r="R48" t="n">
-        <v>7045262</v>
+        <v>7045356</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6062,19 +6053,9 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6089,22 +6070,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123116920</v>
+        <v>123115068</v>
       </c>
       <c r="B49" t="n">
-        <v>78159</v>
+        <v>92264</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6113,25 +6094,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6141,13 +6122,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557888</v>
+        <v>557961</v>
       </c>
       <c r="R49" t="n">
-        <v>7045356</v>
+        <v>7045587</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6174,9 +6155,19 @@
           <t>2025-03-12</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6191,22 +6182,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123115087</v>
+        <v>123117651</v>
       </c>
       <c r="B50" t="n">
-        <v>56691</v>
+        <v>57598</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6219,27 +6210,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6248,10 +6243,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557957</v>
+        <v>557907</v>
       </c>
       <c r="R50" t="n">
-        <v>7045576</v>
+        <v>7045262</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6283,7 +6278,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6293,7 +6288,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6323,7 +6318,7 @@
         <v>123115166</v>
       </c>
       <c r="B51" t="n">
-        <v>78420</v>
+        <v>78426</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6432,10 +6427,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123114354</v>
+        <v>123117683</v>
       </c>
       <c r="B52" t="n">
-        <v>92247</v>
+        <v>78517</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6444,25 +6439,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6472,10 +6467,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557978</v>
+        <v>557966</v>
       </c>
       <c r="R52" t="n">
-        <v>7045589</v>
+        <v>7045239</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6507,7 +6502,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6517,7 +6512,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6544,10 +6539,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123115068</v>
+        <v>123114354</v>
       </c>
       <c r="B53" t="n">
-        <v>92247</v>
+        <v>92264</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557961</v>
+        <v>557978</v>
       </c>
       <c r="R53" t="n">
-        <v>7045587</v>
+        <v>7045589</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6619,7 +6614,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6629,7 +6624,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6656,10 +6651,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123117683</v>
+        <v>123115087</v>
       </c>
       <c r="B54" t="n">
-        <v>78511</v>
+        <v>56697</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6668,38 +6663,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557966</v>
+        <v>557957</v>
       </c>
       <c r="R54" t="n">
-        <v>7045239</v>
+        <v>7045576</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6771,7 +6771,7 @@
         <v>123119791</v>
       </c>
       <c r="B55" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>123660607</v>
       </c>
       <c r="B56" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -5868,10 +5868,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123114009</v>
+        <v>123115087</v>
       </c>
       <c r="B47" t="n">
-        <v>90948</v>
+        <v>56700</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5884,31 +5884,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558050</v>
+        <v>557957</v>
       </c>
       <c r="R47" t="n">
         <v>7045576</v>
@@ -5943,7 +5948,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5953,7 +5958,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5980,10 +5985,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123116920</v>
+        <v>123114354</v>
       </c>
       <c r="B48" t="n">
-        <v>78165</v>
+        <v>92269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5992,25 +5997,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6020,13 +6025,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557888</v>
+        <v>557978</v>
       </c>
       <c r="R48" t="n">
-        <v>7045356</v>
+        <v>7045589</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6053,9 +6058,19 @@
           <t>2025-03-12</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6070,22 +6085,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123115068</v>
+        <v>123117651</v>
       </c>
       <c r="B49" t="n">
-        <v>92264</v>
+        <v>57601</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6098,34 +6113,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557961</v>
+        <v>557907</v>
       </c>
       <c r="R49" t="n">
-        <v>7045587</v>
+        <v>7045262</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6157,7 +6181,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6167,7 +6191,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6194,10 +6218,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123117651</v>
+        <v>123119791</v>
       </c>
       <c r="B50" t="n">
-        <v>57598</v>
+        <v>98502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6206,35 +6230,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6243,10 +6262,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557907</v>
+        <v>557988</v>
       </c>
       <c r="R50" t="n">
-        <v>7045262</v>
+        <v>7045172</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6278,7 +6297,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6288,7 +6307,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6315,10 +6334,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123115166</v>
+        <v>123116920</v>
       </c>
       <c r="B51" t="n">
-        <v>78426</v>
+        <v>78170</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6331,21 +6350,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6355,13 +6374,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557961</v>
+        <v>557888</v>
       </c>
       <c r="R51" t="n">
-        <v>7045574</v>
+        <v>7045356</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6388,19 +6407,9 @@
           <t>2025-03-12</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:46</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6415,22 +6424,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123117683</v>
+        <v>123115166</v>
       </c>
       <c r="B52" t="n">
-        <v>78517</v>
+        <v>78431</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6443,21 +6452,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6467,10 +6476,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557966</v>
+        <v>557961</v>
       </c>
       <c r="R52" t="n">
-        <v>7045239</v>
+        <v>7045574</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6502,7 +6511,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6512,7 +6521,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6539,10 +6548,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123114354</v>
+        <v>123114009</v>
       </c>
       <c r="B53" t="n">
-        <v>92264</v>
+        <v>90953</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6555,21 +6564,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6579,10 +6588,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557978</v>
+        <v>558050</v>
       </c>
       <c r="R53" t="n">
-        <v>7045589</v>
+        <v>7045576</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6614,7 +6623,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6624,7 +6633,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6651,10 +6660,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123115087</v>
+        <v>123117683</v>
       </c>
       <c r="B54" t="n">
-        <v>56697</v>
+        <v>78522</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6663,43 +6672,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557957</v>
+        <v>557966</v>
       </c>
       <c r="R54" t="n">
-        <v>7045576</v>
+        <v>7045239</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6731,7 +6735,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6741,7 +6745,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6768,10 +6772,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123119791</v>
+        <v>123115068</v>
       </c>
       <c r="B55" t="n">
-        <v>98396</v>
+        <v>92269</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6780,42 +6784,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557988</v>
+        <v>557961</v>
       </c>
       <c r="R55" t="n">
-        <v>7045172</v>
+        <v>7045587</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6887,7 +6887,7 @@
         <v>123660607</v>
       </c>
       <c r="B56" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -5868,10 +5868,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123115087</v>
+        <v>123115068</v>
       </c>
       <c r="B47" t="n">
-        <v>56700</v>
+        <v>92271</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5884,39 +5884,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557957</v>
+        <v>557961</v>
       </c>
       <c r="R47" t="n">
-        <v>7045576</v>
+        <v>7045587</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5948,7 +5943,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5958,7 +5953,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5985,10 +5980,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123114354</v>
+        <v>123117683</v>
       </c>
       <c r="B48" t="n">
-        <v>92269</v>
+        <v>78524</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5997,25 +5992,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6025,10 +6020,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557978</v>
+        <v>557966</v>
       </c>
       <c r="R48" t="n">
-        <v>7045589</v>
+        <v>7045239</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6060,7 +6055,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6070,7 +6065,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6097,10 +6092,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123117651</v>
+        <v>123114354</v>
       </c>
       <c r="B49" t="n">
-        <v>57601</v>
+        <v>92271</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6113,43 +6108,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557907</v>
+        <v>557978</v>
       </c>
       <c r="R49" t="n">
-        <v>7045262</v>
+        <v>7045589</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6181,7 +6167,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6191,7 +6177,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6218,10 +6204,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123119791</v>
+        <v>123114009</v>
       </c>
       <c r="B50" t="n">
-        <v>98502</v>
+        <v>90955</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6230,42 +6216,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>557988</v>
+        <v>558050</v>
       </c>
       <c r="R50" t="n">
-        <v>7045172</v>
+        <v>7045576</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6297,7 +6279,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6307,7 +6289,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6337,7 +6319,7 @@
         <v>123116920</v>
       </c>
       <c r="B51" t="n">
-        <v>78170</v>
+        <v>78172</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6436,10 +6418,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123115166</v>
+        <v>123115087</v>
       </c>
       <c r="B52" t="n">
-        <v>78431</v>
+        <v>56700</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6448,38 +6430,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557961</v>
+        <v>557957</v>
       </c>
       <c r="R52" t="n">
-        <v>7045574</v>
+        <v>7045576</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6511,7 +6498,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6521,7 +6508,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6548,10 +6535,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123114009</v>
+        <v>123115166</v>
       </c>
       <c r="B53" t="n">
-        <v>90953</v>
+        <v>78433</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6560,25 +6547,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6588,10 +6575,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558050</v>
+        <v>557961</v>
       </c>
       <c r="R53" t="n">
-        <v>7045576</v>
+        <v>7045574</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6623,7 +6610,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6633,7 +6620,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6660,10 +6647,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123117683</v>
+        <v>123117651</v>
       </c>
       <c r="B54" t="n">
-        <v>78522</v>
+        <v>57602</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6672,38 +6659,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557966</v>
+        <v>557907</v>
       </c>
       <c r="R54" t="n">
-        <v>7045239</v>
+        <v>7045262</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6735,7 +6731,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6745,7 +6741,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6772,10 +6768,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123115068</v>
+        <v>123119791</v>
       </c>
       <c r="B55" t="n">
-        <v>92269</v>
+        <v>98504</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6784,38 +6780,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557961</v>
+        <v>557988</v>
       </c>
       <c r="R55" t="n">
-        <v>7045587</v>
+        <v>7045172</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6887,7 +6887,7 @@
         <v>123660607</v>
       </c>
       <c r="B56" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6887,7 +6887,7 @@
         <v>123660607</v>
       </c>
       <c r="B56" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6993,6 +6993,360 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125508568</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>557946</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7045379</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125508711</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>557919</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7045332</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125508787</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>557923</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7045323</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6995,7 +6995,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125508568</v>
+        <v>125508787</v>
       </c>
       <c r="B57" t="n">
         <v>98269</v>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557946</v>
+        <v>557923</v>
       </c>
       <c r="R57" t="n">
-        <v>7045379</v>
+        <v>7045323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7228,7 +7228,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125508787</v>
+        <v>125508568</v>
       </c>
       <c r="B59" t="n">
         <v>98269</v>
@@ -7263,7 +7263,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7277,10 +7277,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557923</v>
+        <v>557946</v>
       </c>
       <c r="R59" t="n">
-        <v>7045323</v>
+        <v>7045379</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7346,6 +7346,116 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>123944837</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57793</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stor-grössjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>557923</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7045440</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6995,7 +6995,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125508787</v>
+        <v>125508568</v>
       </c>
       <c r="B57" t="n">
         <v>98269</v>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557923</v>
+        <v>557946</v>
       </c>
       <c r="R57" t="n">
-        <v>7045323</v>
+        <v>7045379</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7116,7 +7116,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125508711</v>
+        <v>125508787</v>
       </c>
       <c r="B58" t="n">
         <v>98269</v>
@@ -7149,20 +7149,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557919</v>
+        <v>557923</v>
       </c>
       <c r="R58" t="n">
-        <v>7045332</v>
+        <v>7045323</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7191,7 +7200,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7201,7 +7210,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7228,7 +7237,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125508568</v>
+        <v>125508711</v>
       </c>
       <c r="B59" t="n">
         <v>98269</v>
@@ -7261,29 +7270,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557946</v>
+        <v>557919</v>
       </c>
       <c r="R59" t="n">
-        <v>7045379</v>
+        <v>7045332</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6995,15 +6995,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125508568</v>
+        <v>125508711</v>
       </c>
       <c r="B57" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7028,29 +7023,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557946</v>
+        <v>557919</v>
       </c>
       <c r="R57" t="n">
-        <v>7045379</v>
+        <v>7045332</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7079,7 +7065,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7089,7 +7075,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7119,12 +7105,7 @@
         <v>125508787</v>
       </c>
       <c r="B58" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7237,15 +7218,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125508711</v>
+        <v>125508568</v>
       </c>
       <c r="B59" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7270,20 +7246,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557919</v>
+        <v>557946</v>
       </c>
       <c r="R59" t="n">
-        <v>7045332</v>
+        <v>7045379</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7312,7 +7297,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7322,7 +7307,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7352,12 +7337,7 @@
         <v>123944837</v>
       </c>
       <c r="B60" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6998,7 +6998,7 @@
         <v>125508711</v>
       </c>
       <c r="B57" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>125508787</v>
       </c>
       <c r="B58" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>125508568</v>
       </c>
       <c r="B59" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6998,7 +6998,7 @@
         <v>125508711</v>
       </c>
       <c r="B57" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>125508787</v>
       </c>
       <c r="B58" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>125508568</v>
       </c>
       <c r="B59" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6998,7 +6998,7 @@
         <v>125508711</v>
       </c>
       <c r="B57" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>125508787</v>
       </c>
       <c r="B58" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>125508568</v>
       </c>
       <c r="B59" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6998,7 +6998,7 @@
         <v>125508711</v>
       </c>
       <c r="B57" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>125508787</v>
       </c>
       <c r="B58" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>125508568</v>
       </c>
       <c r="B59" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6998,7 +6998,7 @@
         <v>125508711</v>
       </c>
       <c r="B57" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>125508787</v>
       </c>
       <c r="B58" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>125508568</v>
       </c>
       <c r="B59" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>123944837</v>
       </c>
       <c r="B60" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6998,7 +6998,7 @@
         <v>125508711</v>
       </c>
       <c r="B57" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>125508787</v>
       </c>
       <c r="B58" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>125508568</v>
       </c>
       <c r="B59" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7437,6 +7437,233 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129275227</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>557924</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7045312</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129275208</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>557922</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7045291</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7442,7 +7442,7 @@
         <v>129275227</v>
       </c>
       <c r="B61" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7442,7 +7442,7 @@
         <v>129275227</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7442,7 +7442,7 @@
         <v>129275227</v>
       </c>
       <c r="B61" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -7442,7 +7442,7 @@
         <v>129275227</v>
       </c>
       <c r="B61" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>129275208</v>
       </c>
       <c r="B62" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -6515,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="AE52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122887465</v>
+        <v>123115166</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558046</v>
+        <v>557961</v>
       </c>
       <c r="R2" t="n">
-        <v>7045577</v>
+        <v>7045574</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122883141</v>
+        <v>122909987</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>557872</v>
+        <v>558129</v>
       </c>
       <c r="R3" t="n">
-        <v>7045237</v>
+        <v>7045578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,27 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>+50 Ringhack på tall</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,49 +877,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122883501</v>
+        <v>122912661</v>
       </c>
       <c r="B4" t="n">
-        <v>92247</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557908</v>
+        <v>558113</v>
       </c>
       <c r="R4" t="n">
-        <v>7045230</v>
+        <v>7045372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,71 +984,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122885158</v>
+        <v>122912795</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557925</v>
+        <v>558128</v>
       </c>
       <c r="R5" t="n">
-        <v>7045226</v>
+        <v>7045377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,27 +1091,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122887288</v>
+        <v>122914868</v>
       </c>
       <c r="B6" t="n">
-        <v>79856</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558116</v>
+        <v>557948</v>
       </c>
       <c r="R6" t="n">
-        <v>7045369</v>
+        <v>7045384</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,27 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122887408</v>
+        <v>122883501</v>
       </c>
       <c r="B7" t="n">
-        <v>79856</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558107</v>
+        <v>557908</v>
       </c>
       <c r="R7" t="n">
-        <v>7045485</v>
+        <v>7045230</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,59 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122882954</v>
+        <v>122914405</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557874</v>
+        <v>557976</v>
       </c>
       <c r="R8" t="n">
-        <v>7045270</v>
+        <v>7045210</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,22 +1382,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122909459</v>
+        <v>123114354</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,39 +1435,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557966</v>
+        <v>557978</v>
       </c>
       <c r="R9" t="n">
-        <v>7045501</v>
+        <v>7045589</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,27 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,27 +1519,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122908038</v>
+        <v>123115068</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,39 +1542,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558017</v>
+        <v>557961</v>
       </c>
       <c r="R10" t="n">
-        <v>7045654</v>
+        <v>7045587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,27 +1596,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,15 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122914308</v>
+        <v>122914606</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1771,7 +1673,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557955</v>
+        <v>557893</v>
       </c>
       <c r="R11" t="n">
         <v>7045351</v>
@@ -1806,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1816,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,37 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122908738</v>
+        <v>123114009</v>
       </c>
       <c r="B12" t="n">
-        <v>79862</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558014</v>
+        <v>558050</v>
       </c>
       <c r="R12" t="n">
-        <v>7045616</v>
+        <v>7045576</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,22 +1810,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,27 +1840,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122908532</v>
+        <v>122887465</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1971,38 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557942</v>
+        <v>558046</v>
       </c>
       <c r="R13" t="n">
-        <v>7045683</v>
+        <v>7045577</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2029,22 +1917,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,31 +1947,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122909723</v>
+        <v>122908377</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2107,14 +1990,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558113</v>
+        <v>557960</v>
       </c>
       <c r="R14" t="n">
-        <v>7045588</v>
+        <v>7045662</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2156,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,54 +2066,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122908246</v>
+        <v>122908447</v>
       </c>
       <c r="B15" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557977</v>
+        <v>557958</v>
       </c>
       <c r="R15" t="n">
-        <v>7045628</v>
+        <v>7045677</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2262,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,15 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122914413</v>
+        <v>122908666</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,38 +2184,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557884</v>
+        <v>557951</v>
       </c>
       <c r="R16" t="n">
-        <v>7045302</v>
+        <v>7045711</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2388,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,55 +2280,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122908440</v>
+        <v>122909723</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>557960</v>
+        <v>558113</v>
       </c>
       <c r="R17" t="n">
-        <v>7045650</v>
+        <v>7045588</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,12 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,67 +2375,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122909331</v>
+        <v>122910281</v>
       </c>
       <c r="B18" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>557986</v>
+        <v>558178</v>
       </c>
       <c r="R18" t="n">
-        <v>7045500</v>
+        <v>7045498</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2617,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2627,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,67 +2482,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122908559</v>
+        <v>122914213</v>
       </c>
       <c r="B19" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>557959</v>
+        <v>557991</v>
       </c>
       <c r="R19" t="n">
-        <v>7045628</v>
+        <v>7045335</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2734,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2744,12 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2764,67 +2589,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122909049</v>
+        <v>122914308</v>
       </c>
       <c r="B20" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558048</v>
+        <v>557955</v>
       </c>
       <c r="R20" t="n">
-        <v>7045527</v>
+        <v>7045351</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2856,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2866,12 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2886,49 +2696,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122912795</v>
+        <v>122914334</v>
       </c>
       <c r="B21" t="n">
-        <v>82568</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2938,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558128</v>
+        <v>557931</v>
       </c>
       <c r="R21" t="n">
-        <v>7045377</v>
+        <v>7045323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2983,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,37 +2815,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122914606</v>
+        <v>122914531</v>
       </c>
       <c r="B22" t="n">
-        <v>91003</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3050,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>557893</v>
+        <v>557870</v>
       </c>
       <c r="R22" t="n">
-        <v>7045351</v>
+        <v>7045346</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3085,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3095,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3122,45 +2922,35 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122914666</v>
+        <v>122914573</v>
       </c>
       <c r="B23" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
@@ -3170,7 +2960,7 @@
         <v>557892</v>
       </c>
       <c r="R23" t="n">
-        <v>7045356</v>
+        <v>7045361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3202,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3212,12 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3244,57 +3029,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122908779</v>
+        <v>123116920</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>557996</v>
+        <v>557888</v>
       </c>
       <c r="R24" t="n">
-        <v>7045609</v>
+        <v>7045356</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3318,22 +3094,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,49 +3114,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122914405</v>
+        <v>123117683</v>
       </c>
       <c r="B25" t="n">
-        <v>92264</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3400,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>557976</v>
+        <v>557966</v>
       </c>
       <c r="R25" t="n">
-        <v>7045210</v>
+        <v>7045239</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3430,22 +3191,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3460,27 +3221,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122908666</v>
+        <v>122882613</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,34 +3244,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>557951</v>
+        <v>557881</v>
       </c>
       <c r="R26" t="n">
-        <v>7045711</v>
+        <v>7045420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3542,22 +3298,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3572,27 +3328,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122914531</v>
+        <v>122887288</v>
       </c>
       <c r="B27" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3624,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>557870</v>
+        <v>558116</v>
       </c>
       <c r="R27" t="n">
-        <v>7045346</v>
+        <v>7045369</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3654,22 +3405,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3684,27 +3435,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122914213</v>
+        <v>122887408</v>
       </c>
       <c r="B28" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,21 +3458,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3736,10 +3482,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>557991</v>
+        <v>558107</v>
       </c>
       <c r="R28" t="n">
-        <v>7045335</v>
+        <v>7045485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3766,22 +3512,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3796,27 +3542,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122909860</v>
+        <v>122908556</v>
       </c>
       <c r="B29" t="n">
-        <v>79862</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3844,14 +3585,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558133</v>
+        <v>557917</v>
       </c>
       <c r="R29" t="n">
-        <v>7045474</v>
+        <v>7045695</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3883,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3893,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3908,66 +3649,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122913820</v>
+        <v>122908587</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558157</v>
+        <v>557921</v>
       </c>
       <c r="R30" t="n">
-        <v>7045329</v>
+        <v>7045688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3999,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4009,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4036,59 +3768,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122908497</v>
+        <v>122908738</v>
       </c>
       <c r="B31" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>557969</v>
+        <v>558014</v>
       </c>
       <c r="R31" t="n">
-        <v>7045641</v>
+        <v>7045616</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4120,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4130,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4157,15 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122910281</v>
+        <v>122909860</v>
       </c>
       <c r="B32" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,34 +3886,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558178</v>
+        <v>558133</v>
       </c>
       <c r="R32" t="n">
-        <v>7045498</v>
+        <v>7045474</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4232,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4242,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4257,27 +3970,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122914334</v>
+        <v>122910006</v>
       </c>
       <c r="B33" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4285,21 +3993,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4309,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>557931</v>
+        <v>558154</v>
       </c>
       <c r="R33" t="n">
-        <v>7045323</v>
+        <v>7045445</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4344,7 +4052,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4354,7 +4062,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4369,27 +4077,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122908377</v>
+        <v>122911743</v>
       </c>
       <c r="B34" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4397,34 +4100,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>557960</v>
+        <v>558114</v>
       </c>
       <c r="R34" t="n">
-        <v>7045662</v>
+        <v>7045374</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4456,7 +4159,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4466,7 +4169,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4481,62 +4184,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122910006</v>
+        <v>122909331</v>
       </c>
       <c r="B35" t="n">
-        <v>79862</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558154</v>
+        <v>557986</v>
       </c>
       <c r="R35" t="n">
-        <v>7045445</v>
+        <v>7045500</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4568,7 +4271,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4578,7 +4281,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4605,15 +4308,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122914573</v>
+        <v>122883141</v>
       </c>
       <c r="B36" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4621,34 +4319,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>557892</v>
+        <v>557872</v>
       </c>
       <c r="R36" t="n">
-        <v>7045361</v>
+        <v>7045237</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4675,22 +4378,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>+50 Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4705,27 +4413,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122914868</v>
+        <v>122908038</v>
       </c>
       <c r="B37" t="n">
-        <v>79863</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,34 +4436,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>557948</v>
+        <v>558017</v>
       </c>
       <c r="R37" t="n">
-        <v>7045384</v>
+        <v>7045654</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4792,7 +4500,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4802,7 +4510,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4829,15 +4542,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122908422</v>
+        <v>122908246</v>
       </c>
       <c r="B38" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4862,22 +4570,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
         <v>557977</v>
       </c>
       <c r="R38" t="n">
-        <v>7045673</v>
+        <v>7045628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4909,7 +4616,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4919,12 +4626,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4951,15 +4653,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122911743</v>
+        <v>122908422</v>
       </c>
       <c r="B39" t="n">
-        <v>79862</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4967,34 +4664,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558114</v>
+        <v>557977</v>
       </c>
       <c r="R39" t="n">
-        <v>7045374</v>
+        <v>7045673</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5026,7 +4728,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5036,7 +4738,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5051,71 +4758,62 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122909181</v>
+        <v>122908440</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558033</v>
+        <v>557960</v>
       </c>
       <c r="R40" t="n">
-        <v>7045487</v>
+        <v>7045650</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5147,7 +4845,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5157,7 +4855,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5184,15 +4887,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122908447</v>
+        <v>122908559</v>
       </c>
       <c r="B41" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5200,34 +4898,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>557958</v>
+        <v>557959</v>
       </c>
       <c r="R41" t="n">
-        <v>7045677</v>
+        <v>7045628</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5259,7 +4962,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5269,7 +4972,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5284,27 +4992,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122909987</v>
+        <v>122909049</v>
       </c>
       <c r="B42" t="n">
-        <v>90983</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,34 +5015,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558129</v>
+        <v>558048</v>
       </c>
       <c r="R42" t="n">
-        <v>7045578</v>
+        <v>7045527</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5371,7 +5079,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5381,7 +5089,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5396,54 +5109,50 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122908181</v>
+        <v>122909459</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5452,10 +5161,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>557989</v>
+        <v>557966</v>
       </c>
       <c r="R43" t="n">
-        <v>7045623</v>
+        <v>7045501</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5487,7 +5196,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5497,7 +5206,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5512,66 +5226,62 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122908146</v>
+        <v>122910499</v>
       </c>
       <c r="B44" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lilltjärnen, Lilltjärnen, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>557988</v>
+        <v>558200</v>
       </c>
       <c r="R44" t="n">
-        <v>7045659</v>
+        <v>7045484</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5603,7 +5313,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5613,7 +5323,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5628,66 +5343,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122909523</v>
+        <v>122914666</v>
       </c>
       <c r="B45" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grössjörået, Grössjörået, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558123</v>
+        <v>557892</v>
       </c>
       <c r="R45" t="n">
-        <v>7045531</v>
+        <v>7045356</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5719,7 +5430,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5729,7 +5440,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5756,50 +5472,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122912661</v>
+        <v>123115087</v>
       </c>
       <c r="B46" t="n">
-        <v>82568</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558113</v>
+        <v>557957</v>
       </c>
       <c r="R46" t="n">
-        <v>7045372</v>
+        <v>7045576</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5826,29 +5542,29 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG46" t="b">
         <v>0</v>
@@ -5868,53 +5584,56 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123115068</v>
+        <v>123944837</v>
       </c>
       <c r="B47" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Stor-grössjön, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>557961</v>
+        <v>557923</v>
       </c>
       <c r="R47" t="n">
-        <v>7045587</v>
+        <v>7045440</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5938,22 +5657,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:40</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5968,27 +5677,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123117683</v>
+        <v>129275227</v>
       </c>
       <c r="B48" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5996,34 +5700,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>557966</v>
+        <v>557924</v>
       </c>
       <c r="R48" t="n">
-        <v>7045239</v>
+        <v>7045312</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6050,22 +5763,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6092,50 +5805,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123114354</v>
+        <v>123117651</v>
       </c>
       <c r="B49" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>557978</v>
+        <v>557907</v>
       </c>
       <c r="R49" t="n">
-        <v>7045589</v>
+        <v>7045262</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6167,7 +5884,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6177,7 +5894,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6204,50 +5921,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123114009</v>
+        <v>122882954</v>
       </c>
       <c r="B50" t="n">
-        <v>90955</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558050</v>
+        <v>557874</v>
       </c>
       <c r="R50" t="n">
-        <v>7045576</v>
+        <v>7045270</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6274,22 +5995,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6304,65 +6025,69 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123116920</v>
+        <v>122885158</v>
       </c>
       <c r="B51" t="n">
-        <v>78172</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>557888</v>
+        <v>557925</v>
       </c>
       <c r="R51" t="n">
-        <v>7045356</v>
+        <v>7045226</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6386,12 +6111,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6406,67 +6141,61 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123115087</v>
+        <v>122908146</v>
       </c>
       <c r="B52" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>557957</v>
+        <v>557988</v>
       </c>
       <c r="R52" t="n">
-        <v>7045576</v>
+        <v>7045659</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6493,29 +6222,29 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
@@ -6535,50 +6264,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123115166</v>
+        <v>122908181</v>
       </c>
       <c r="B53" t="n">
-        <v>78433</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>557961</v>
+        <v>557989</v>
       </c>
       <c r="R53" t="n">
-        <v>7045574</v>
+        <v>7045623</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6605,22 +6333,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6647,59 +6375,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123117651</v>
+        <v>122908497</v>
       </c>
       <c r="B54" t="n">
-        <v>57602</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>557907</v>
+        <v>557969</v>
       </c>
       <c r="R54" t="n">
-        <v>7045262</v>
+        <v>7045641</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6726,22 +6449,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6756,27 +6479,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123119791</v>
+        <v>122908532</v>
       </c>
       <c r="B55" t="n">
-        <v>98504</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6803,19 +6521,19 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Lilltjärnen, Lilltjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>557988</v>
+        <v>557942</v>
       </c>
       <c r="R55" t="n">
-        <v>7045172</v>
+        <v>7045683</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6842,22 +6560,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6884,15 +6602,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123660607</v>
+        <v>122908779</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6919,12 +6632,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6933,10 +6641,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>557960</v>
+        <v>557996</v>
       </c>
       <c r="R56" t="n">
-        <v>7045324</v>
+        <v>7045609</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6963,12 +6671,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6983,22 +6701,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125508711</v>
+        <v>122909181</v>
       </c>
       <c r="B57" t="n">
-        <v>98343</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7023,20 +6741,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>557919</v>
+        <v>558033</v>
       </c>
       <c r="R57" t="n">
-        <v>7045332</v>
+        <v>7045487</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7060,22 +6787,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7090,22 +6817,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125508787</v>
+        <v>122909523</v>
       </c>
       <c r="B58" t="n">
-        <v>98343</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7132,24 +6859,19 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lillfjället, Lillfjället, Ång</t>
+          <t>Grössjörået, Grössjörået, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>557923</v>
+        <v>558123</v>
       </c>
       <c r="R58" t="n">
-        <v>7045323</v>
+        <v>7045531</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7176,22 +6898,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7206,22 +6928,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125508568</v>
+        <v>122913820</v>
       </c>
       <c r="B59" t="n">
-        <v>98343</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7248,12 +6970,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7262,10 +6979,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>557946</v>
+        <v>558157</v>
       </c>
       <c r="R59" t="n">
-        <v>7045379</v>
+        <v>7045329</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7292,22 +7009,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7322,68 +7039,64 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123944837</v>
+        <v>122914413</v>
       </c>
       <c r="B60" t="n">
-        <v>57812</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stor-grössjön, Ång</t>
+          <t>Lillfjället, Lillfjället, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>557923</v>
+        <v>557884</v>
       </c>
       <c r="R60" t="n">
-        <v>7045440</v>
+        <v>7045302</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7407,12 +7120,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7427,54 +7150,49 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129275227</v>
+        <v>123119791</v>
       </c>
       <c r="B61" t="n">
-        <v>57896</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7483,10 +7201,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>557924</v>
+        <v>557988</v>
       </c>
       <c r="R61" t="n">
-        <v>7045312</v>
+        <v>7045172</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7513,7 +7231,7 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
@@ -7523,7 +7241,7 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -7555,10 +7273,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129275208</v>
+        <v>123660607</v>
       </c>
       <c r="B62" t="n">
-        <v>98769</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7585,7 +7303,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7594,10 +7317,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>557922</v>
+        <v>557960</v>
       </c>
       <c r="R62" t="n">
-        <v>7045291</v>
+        <v>7045324</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7624,22 +7347,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>16:06</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>16:06</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7654,15 +7367,465 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125508568</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>557946</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7045379</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125508711</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>557919</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7045332</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125508787</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>557923</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7045323</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129275208</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lillfjället, Lillfjället, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>557922</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7045291</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19347-2024 artfynd.xlsx
+++ b/artfynd/A 19347-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123115166</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909987</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122912661</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122912795</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914868</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122883501</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914405</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123114354</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123115068</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914606</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123114009</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122887465</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908377</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908447</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908666</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909723</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910281</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914213</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914308</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914334</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914531</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914573</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3123,6 +3238,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123116920</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3230,6 +3350,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123117683</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3337,6 +3462,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122882613</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3444,6 +3574,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122887288</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3551,6 +3686,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122887408</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3658,6 +3798,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908556</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3765,6 +3910,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908587</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3872,6 +4022,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908738</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3979,6 +4134,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909860</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4086,6 +4246,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910006</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4193,6 +4358,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122911743</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4305,6 +4475,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909331</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4422,6 +4597,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122883141</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4539,6 +4719,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908038</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4650,6 +4835,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908246</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4767,6 +4957,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908422</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4884,6 +5079,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908440</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5001,6 +5201,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908559</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5118,6 +5323,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909049</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5235,6 +5445,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909459</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5352,6 +5567,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122910499</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5469,6 +5689,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914666</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5581,6 +5806,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123115087</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5686,6 +5916,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123944837</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5802,6 +6037,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129275227</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5918,6 +6158,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123117651</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6034,6 +6279,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122882954</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6150,6 +6400,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122885158</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6261,6 +6516,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908146</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6372,6 +6632,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908181</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6488,6 +6753,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908497</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6599,6 +6869,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908532</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6710,6 +6985,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122908779</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6826,6 +7106,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909181</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6937,6 +7222,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122909523</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7048,6 +7338,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122913820</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7159,6 +7454,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122914413</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7270,6 +7570,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123119791</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7376,6 +7681,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123660607</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7492,6 +7802,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125508568</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7599,6 +7914,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125508711</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7715,6 +8035,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125508787</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7826,8 +8151,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129275208</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>